--- a/data/trending_integrated_20260911_11.xlsx
+++ b/data/trending_integrated_20260911_11.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16060</v>
+        <v>15400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+29.94%</t>
+          <t>+27.38%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.22</v>
+        <v>3.11</v>
       </c>
       <c r="E2" t="n">
-        <v>113</v>
+        <v>324</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="G2" t="n">
-        <v>89</v>
+        <v>745</v>
       </c>
       <c r="H2" t="n">
-        <v>2.39</v>
+        <v>3.14</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12360</v>
+        <v>12090</v>
       </c>
       <c r="K2" t="n">
-        <v>12800</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>16060</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>12690</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.61</v>
+        <v>0.03</v>
       </c>
       <c r="O2" t="n">
-        <v>205455310605</v>
+        <v>162760000000</v>
       </c>
       <c r="P2" t="n">
-        <v>30550</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-139000</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Nvidia CEO 젠슨 황의 사이버 보안 시장 전망 발언에 힘입어 급등. 양자보안 관련주로 주목받으며 높은 상승률 기록.</t>
+          <t>중동 전쟁 및 국제 유가 급등에 따른 수혜 기대. 3연상 등 단기 급등에 대한 높은 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['사이버 보안', '젠슨 황', '양자보안']</t>
+          <t>['국제유가', '중동전쟁', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2600</v>
+        <v>16060</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+22.35%</t>
+          <t>+27.36%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>47</v>
+        <v>121</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="G3" t="n">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="H3" t="n">
-        <v>3.83</v>
+        <v>2.39</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2125</v>
+        <v>12610</v>
       </c>
       <c r="K3" t="n">
-        <v>2230</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2692</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2170</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.76</v>
+        <v>2.61</v>
       </c>
       <c r="O3" t="n">
-        <v>76864670442</v>
+        <v>205825000000</v>
       </c>
       <c r="P3" t="n">
-        <v>4810</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-913000</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>젠슨 황의 사이버보안 섹터 지목과 함께 양자컴퓨터 보조금 지원 소식 언급. 드림시큐리티의 대장주로서의 부각 및 상승 신호.</t>
+          <t>젠슨 황의 사이버 보안 부문 지목에 따른 보안 섹터 급등. 양자 보안 관련 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['젠슨황', '사이버보안', '양자컴퓨터']</t>
+          <t>['사이버 보안', '젠슨 황', '양자보안']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,12 +735,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>138800</v>
+        <v>140700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+19.35%</t>
+          <t>+21.61%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.26</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G4" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="H4" t="n">
         <v>4.32</v>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>116300</v>
+        <v>115700</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>112100</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>147500</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="N4" t="n">
         <v>4.58</v>
       </c>
       <c r="O4" t="n">
-        <v>394880000000</v>
+        <v>405333199100</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>196800</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>27750</v>
       </c>
       <c r="R4" t="n">
-        <v>75000</v>
+        <v>52000</v>
       </c>
       <c r="S4" t="n">
-        <v>87000</v>
+        <v>96000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>애플 관련주 또는 무라타 제작소와의 연관성으로 상승했으나, 단기 급등 후 차익 실현 매물이 출현함.</t>
+          <t>애플 및 무라타 관련 호재로 인한 급등세. 손바뀜 및 단기 급등에 대한 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['애플', '무라타 제작소', '손바뀜']</t>
+          <t>['애플', '급등', '손바뀜']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7850</v>
+        <v>2580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+17.16%</t>
+          <t>+20.84%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.79</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
         <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>127</v>
+        <v>59</v>
       </c>
       <c r="H5" t="n">
-        <v>2.15</v>
+        <v>3.83</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6700</v>
+        <v>2135</v>
       </c>
       <c r="K5" t="n">
-        <v>6530</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>8370</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>6430</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.94</v>
+        <v>3.76</v>
       </c>
       <c r="O5" t="n">
-        <v>92181060675</v>
+        <v>80256000000</v>
       </c>
       <c r="P5" t="n">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1206</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>146000</v>
+        <v>-1884000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광통신 및 위성네트워크 섹터 내 우리로의 대장주 역할 부각. 양자주로서의 재료 풍부 및 13,000원 이상의 목표가 제시.</t>
+          <t>젠슨 황의 사이버보안 섹터 지목과 함께 양자컴퓨터 보조금 지원 소식 언급. 드림시큐리티의 대장주로서의 부각 및 상승 신호.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '양자주', '대장주']</t>
+          <t>['젠슨황', '사이버보안', '양자컴퓨터']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8300</v>
+        <v>8010</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+11.86%</t>
+          <t>+19.55%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.12</v>
+        <v>-0.79</v>
       </c>
       <c r="E6" t="n">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="G6" t="n">
-        <v>571</v>
+        <v>138</v>
       </c>
       <c r="H6" t="n">
-        <v>1.29</v>
+        <v>2.15</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,143 +963,143 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7420</v>
+        <v>6700</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>6530</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>8370</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>6430</v>
       </c>
       <c r="N6" t="n">
-        <v>1.17</v>
+        <v>2.94</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>102385654175</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1206</v>
       </c>
       <c r="R6" t="n">
-        <v>20000</v>
+        <v>141000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>9월 14일 예정된 WCLC 학회에서의 임상 데이터 발표에 대한 기대감. 기술 수출 가능성과 함께 긍정적 전망.</t>
+          <t>광통신 및 위성네트워크 섹터 내 우리로의 대장주 역할 부각. 양자주로서의 재료 풍부 및 13,000원 이상의 목표가 제시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['임상 데이터', 'WCLC', '기술 수출']</t>
+          <t>['광통신', '양자주', '대장주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7680</v>
+        <v>27500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+5.36%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>95</v>
+        <v>207</v>
       </c>
       <c r="F7" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>287</v>
+        <v>324</v>
       </c>
       <c r="H7" t="n">
-        <v>11.72</v>
+        <v>0.32</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7100</v>
+        <v>26100</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>26350</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>30300</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>25400</v>
       </c>
       <c r="N7" t="n">
-        <v>11.62</v>
+        <v>0.33</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>273569020950</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>39350</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="R7" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>외국인/기관의 평균 매매 단가 분석과 함께 주가 반등 기대감이 존재하나, 지수 하락 영향 및 단기 매매 전략에 대한 논의.</t>
+          <t>하락장 속에서 상대적으로 선방하며 자금이 유입되는 모습. '절대반지'라는 별칭과 함께 빠른 시세 상승 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['외국인/기관', '매매 단가', '주가 반등']</t>
+          <t>['하락장', '자금 유입', '상승 기대감']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,86 +1108,86 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9890</v>
+        <v>51000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+6.57%</t>
+          <t>+1.19%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="F8" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>222</v>
+        <v>448</v>
       </c>
       <c r="H8" t="n">
-        <v>4.49</v>
+        <v>38.78</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9280</v>
+        <v>50400</v>
       </c>
       <c r="K8" t="n">
-        <v>10030</v>
+        <v>50500</v>
       </c>
       <c r="L8" t="n">
-        <v>10880</v>
+        <v>51100</v>
       </c>
       <c r="M8" t="n">
-        <v>9800</v>
+        <v>49650</v>
       </c>
       <c r="N8" t="n">
-        <v>4.42</v>
+        <v>38.69</v>
       </c>
       <c r="O8" t="n">
-        <v>19653431540</v>
+        <v>46068681425</v>
       </c>
       <c r="P8" t="n">
-        <v>15640</v>
+        <v>67300</v>
       </c>
       <c r="Q8" t="n">
-        <v>5470</v>
+        <v>23150</v>
       </c>
       <c r="R8" t="n">
-        <v>-41000</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
+          <t>사우디아라비아 등에서 약 4.7조원 규모의 대형 수주 공시. 겹호재와 상승 추세 속에서 추가 상승 기대감 형성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
+          <t>['대형 수주', '공시', '상승 추세']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,95 +1195,95 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15340</v>
+        <v>1923</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.72%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3.11</v>
+        <v>0.32</v>
       </c>
       <c r="E9" t="n">
-        <v>313</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>184</v>
+        <v>52</v>
       </c>
       <c r="G9" t="n">
-        <v>697</v>
+        <v>144</v>
       </c>
       <c r="H9" t="n">
-        <v>3.14</v>
+        <v>2.44</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14510</v>
+        <v>1901</v>
       </c>
       <c r="K9" t="n">
-        <v>17010</v>
+        <v>2050</v>
       </c>
       <c r="L9" t="n">
-        <v>17310</v>
+        <v>2080</v>
       </c>
       <c r="M9" t="n">
-        <v>15310</v>
+        <v>1909</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>161508839160</v>
+        <v>36863613589</v>
       </c>
       <c r="P9" t="n">
-        <v>36200</v>
+        <v>4795</v>
       </c>
       <c r="Q9" t="n">
-        <v>8920</v>
+        <v>1524</v>
       </c>
       <c r="R9" t="n">
-        <v>-347000</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>중동 전쟁 및 국제 유가 폭등으로 인한 3연상 기대감. WTI 100달러 돌파 및 추가 상승 가능성 언급.</t>
+          <t>홍해 사태와 유가 상승 전망에 따른 전쟁 테마주 관심 증가. 그러나 명확한 근거 부족.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['흥구석유', '국제 유가', '중동 전쟁']</t>
+          <t>['홍해', '유가', '전쟁테마주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,130 +1292,130 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27450</v>
+        <v>53800</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.17%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>-0.44</v>
       </c>
       <c r="E10" t="n">
-        <v>196</v>
+        <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>310</v>
+        <v>110</v>
       </c>
       <c r="H10" t="n">
-        <v>0.32</v>
+        <v>2.92</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>26100</v>
+        <v>53200</v>
       </c>
       <c r="K10" t="n">
-        <v>26350</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>30300</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>25400</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.33</v>
+        <v>3.36</v>
       </c>
       <c r="O10" t="n">
-        <v>264322980475</v>
+        <v>74889000000</v>
       </c>
       <c r="P10" t="n">
-        <v>39350</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>하락장 속에서 상대적으로 선방하며 자금이 유입되는 모습. '절대반지'라는 별칭과 함께 빠른 시세 상승 기대감.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['하락장', '자금 유입', '상승 기대감']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19700</v>
+        <v>90400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.29%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="E11" t="n">
+        <v>168</v>
+      </c>
+      <c r="F11" t="n">
         <v>104</v>
       </c>
-      <c r="F11" t="n">
-        <v>68</v>
-      </c>
       <c r="G11" t="n">
-        <v>352</v>
+        <v>712</v>
       </c>
       <c r="H11" t="n">
-        <v>10.65</v>
+        <v>23.59</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>19450</v>
+        <v>89900</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>88700</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>90400</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="N11" t="n">
-        <v>10.64</v>
+        <v>23.65</v>
       </c>
       <c r="O11" t="n">
-        <v>65491000000</v>
+        <v>95154336650</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>-249000</v>
+        <v>-264000</v>
       </c>
       <c r="S11" t="n">
-        <v>-8000</v>
+        <v>26000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>NH투자증권의 목표주가 상향 리포트와 함께 '대차해지'를 통한 공매도 세력 대응 요구가 지배적. 신규 투자자에게 '대차해지' 참여 독려.</t>
+          <t>미국 에너지 투자 협상 마무리 및 원전 사업 수주 기대감. 수주 잔고 증가에 따른 상승 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['대차해지', '목표주가 상향', '공매도']</t>
+          <t>['원전', '수주', '에너지']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53800</v>
+        <v>3635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.44</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G12" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="H12" t="n">
-        <v>2.92</v>
+        <v>0.73</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>53200</v>
+        <v>3620</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3725</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3915</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3550</v>
       </c>
       <c r="N12" t="n">
-        <v>3.36</v>
+        <v>1.54</v>
       </c>
       <c r="O12" t="n">
-        <v>72697000000</v>
+        <v>36517568946</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>4335</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="R12" t="n">
-        <v>-14000</v>
+        <v>64000</v>
       </c>
       <c r="S12" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1917</v>
+        <v>416500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.84%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="E13" t="n">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="F13" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>143</v>
+        <v>201</v>
       </c>
       <c r="H13" t="n">
-        <v>2.44</v>
+        <v>38.02</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1901</v>
+        <v>415500</v>
       </c>
       <c r="K13" t="n">
-        <v>2050</v>
+        <v>407000</v>
       </c>
       <c r="L13" t="n">
-        <v>2080</v>
+        <v>418000</v>
       </c>
       <c r="M13" t="n">
-        <v>1909</v>
+        <v>404000</v>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>37.82</v>
       </c>
       <c r="O13" t="n">
-        <v>36515762835</v>
+        <v>37789595250</v>
       </c>
       <c r="P13" t="n">
-        <v>4795</v>
+        <v>822000</v>
       </c>
       <c r="Q13" t="n">
-        <v>1524</v>
+        <v>283000</v>
       </c>
       <c r="R13" t="n">
-        <v>-1017000</v>
+        <v>13000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>홍해 사태로 인한 유가 상승 기대감 속에서 장금상선과 함께 전쟁 테마주로 분류. 단기적인 변동성 및 매수/매도 의견이 혼재.</t>
+          <t>로봇 사업 확장 및 아틀라스 관절 부품 수주. 유럽 중국차 관세 관련 반사이익 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['홍해 사태', '유가 상승', '전쟁 테마주']</t>
+          <t>['로봇', '수주', '관세']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>417000</v>
+        <v>19620</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-0.66%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="G14" t="n">
-        <v>198</v>
+        <v>373</v>
       </c>
       <c r="H14" t="n">
-        <v>38.02</v>
+        <v>10.65</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>415500</v>
+        <v>19750</v>
       </c>
       <c r="K14" t="n">
-        <v>407000</v>
+        <v>19500</v>
       </c>
       <c r="L14" t="n">
-        <v>417500</v>
+        <v>19840</v>
       </c>
       <c r="M14" t="n">
-        <v>404000</v>
+        <v>19060</v>
       </c>
       <c r="N14" t="n">
-        <v>37.82</v>
+        <v>10.64</v>
       </c>
       <c r="O14" t="n">
-        <v>35458282750</v>
+        <v>68652679475</v>
       </c>
       <c r="P14" t="n">
-        <v>822000</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>283000</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>현대모비스, 아틀라스 관절 부품 전량 수주 및 그룹사 양산 로드맵 가동. 유럽 및 중국차 관세 부과 관련 호재 기대. 미래차 및 로봇 신기술 60종 공개.</t>
+          <t>대차 해지 독려 및 공매도 대응 촉구. 목표가 상향 뉴스와 신규 수주 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['로봇', '관절 부품', '미래차']</t>
+          <t>['대차해지', '공매도', '목표가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>90000</v>
+        <v>8850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="E15" t="n">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="F15" t="n">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="G15" t="n">
-        <v>701</v>
+        <v>185</v>
       </c>
       <c r="H15" t="n">
-        <v>23.59</v>
+        <v>27.19</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,222 +1791,222 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>89900</v>
+        <v>8970</v>
       </c>
       <c r="K15" t="n">
-        <v>88700</v>
+        <v>8780</v>
       </c>
       <c r="L15" t="n">
-        <v>90400</v>
+        <v>8880</v>
       </c>
       <c r="M15" t="n">
-        <v>88000</v>
+        <v>8680</v>
       </c>
       <c r="N15" t="n">
-        <v>23.65</v>
+        <v>27.16</v>
       </c>
       <c r="O15" t="n">
-        <v>91560721400</v>
+        <v>12080139625</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>57000</v>
+        <v>8120</v>
       </c>
       <c r="R15" t="n">
-        <v>-245000</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 에너지 투자 협상 완료 및 수주 잔고 증가로 인한 기대감 부각. 원전 관련 긍정적 전망 및 목표가 상향 제시.</t>
+          <t>주가 상승에 대한 강한 불만과 함께 회사의 실적 부진 및 저평가에 대한 부정적인 인식이 지배적임.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['에너지', '수주', '원전']</t>
+          <t>['저평가', '실적 부진', '금리 인상']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50400</v>
+        <v>14430</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-2.10%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.09</v>
+        <v>-0.39</v>
       </c>
       <c r="E16" t="n">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="F16" t="n">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
-        <v>444</v>
+        <v>186</v>
       </c>
       <c r="H16" t="n">
-        <v>38.78</v>
+        <v>2.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>50800</v>
+        <v>14740</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>14050</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>14560</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>14030</v>
       </c>
       <c r="N16" t="n">
-        <v>38.69</v>
+        <v>2.89</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>39288197395</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R16" t="n">
-        <v>-110000</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>사우디아라비아 등에서 약 4.7조원 규모의 대형 수주 공시. 겹호재와 상승 추세 속에서 추가 상승 기대감 형성.</t>
+          <t>외국인 매수세 및 프로그램 매수에 따른 상승 기대감 존재. 단기적인 상승 움직임 예측되나, 전반적인 증시 하락 분위기 속에 관망세 짙음.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['대형 수주', '공시', '상승 추세']</t>
+          <t>['외국인', '매수', '움직임']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14850</v>
+        <v>14220</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.26%</t>
+          <t>-2.60%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="E17" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="F17" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G17" t="n">
-        <v>204</v>
+        <v>418</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>15040</v>
+        <v>14600</v>
       </c>
       <c r="K17" t="n">
-        <v>14550</v>
+        <v>14800</v>
       </c>
       <c r="L17" t="n">
-        <v>15260</v>
+        <v>14950</v>
       </c>
       <c r="M17" t="n">
-        <v>14350</v>
+        <v>14020</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="O17" t="n">
-        <v>15222887975</v>
+        <v>72874979345</v>
       </c>
       <c r="P17" t="n">
-        <v>19380</v>
+        <v>30200</v>
       </c>
       <c r="Q17" t="n">
-        <v>3200</v>
+        <v>3540</v>
       </c>
       <c r="R17" t="n">
-        <v>23000</v>
+        <v>-371000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-69000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>금호건설, 호남 반도체 부지 100만평 추가 확보 검토 및 삼성전자 신축 공장 수주 소식. 친환경 및 폐기물 처리 사업 관련 성장성 기대.</t>
+          <t>원전 관련 테마 기대감 속에서 모건 스탠리의 대량 매수 관측. 단기 과열 우려도 있으나, 원전주의 강력한 재료 기반 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['반도체 부지', '신축 공장 수주', '친환경']</t>
+          <t>['원전 테마', '모건 스탠리', '수주']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8810</v>
+        <v>28750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G18" t="n">
-        <v>169</v>
+        <v>114</v>
       </c>
       <c r="H18" t="n">
-        <v>27.19</v>
+        <v>51.28</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>8970</v>
+        <v>29550</v>
       </c>
       <c r="K18" t="n">
-        <v>8780</v>
+        <v>28650</v>
       </c>
       <c r="L18" t="n">
-        <v>8870</v>
+        <v>28900</v>
       </c>
       <c r="M18" t="n">
-        <v>8680</v>
+        <v>28500</v>
       </c>
       <c r="N18" t="n">
-        <v>27.16</v>
+        <v>24.99</v>
       </c>
       <c r="O18" t="n">
-        <v>11290330770</v>
+        <v>31937758875</v>
       </c>
       <c r="P18" t="n">
-        <v>17950</v>
+        <v>31200</v>
       </c>
       <c r="Q18" t="n">
-        <v>8120</v>
+        <v>21000</v>
       </c>
       <c r="R18" t="n">
-        <v>-28000</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-33000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 강한 불만과 함께 회사의 실적 부진 및 저평가에 대한 부정적인 인식이 지배적임.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['저평가', '실적 부진', '금리 인상']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,130 +2120,130 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14420</v>
+        <v>7410</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.17%</t>
+          <t>-3.52%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.39</v>
+        <v>0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="F19" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G19" t="n">
-        <v>159</v>
+        <v>294</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5</v>
+        <v>11.72</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>14740</v>
+        <v>7680</v>
       </c>
       <c r="K19" t="n">
-        <v>14050</v>
+        <v>7540</v>
       </c>
       <c r="L19" t="n">
-        <v>14560</v>
+        <v>7660</v>
       </c>
       <c r="M19" t="n">
-        <v>14030</v>
+        <v>7390</v>
       </c>
       <c r="N19" t="n">
-        <v>2.89</v>
+        <v>11.62</v>
       </c>
       <c r="O19" t="n">
-        <v>36679749920</v>
+        <v>7480398680</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>8850</v>
       </c>
       <c r="Q19" t="n">
-        <v>1272</v>
+        <v>4220</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>43000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>외국인 매수세 및 프로그램 매수에 따른 상승 기대감 존재. 단기적인 상승 움직임 예측되나, 전반적인 증시 하락 분위기 속에 관망세 짙음.</t>
+          <t>기관 매수세 및 주가 반등 기대감과 공매도 우려.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['외국인', '매수', '움직임']</t>
+          <t>['기관매매', '공매도', '주가전망']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>28700</v>
+        <v>1787000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>-3.72%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="E20" t="n">
-        <v>43</v>
+        <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>34</v>
+        <v>467</v>
       </c>
       <c r="G20" t="n">
-        <v>106</v>
+        <v>1136</v>
       </c>
       <c r="H20" t="n">
-        <v>51.27</v>
+        <v>50.55</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,91 +2251,91 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>29550</v>
+        <v>1856000</v>
       </c>
       <c r="K20" t="n">
-        <v>28650</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>28900</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>28500</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>24.99</v>
+        <v>50.67</v>
       </c>
       <c r="O20" t="n">
-        <v>31224661325</v>
+        <v>2085672000000</v>
       </c>
       <c r="P20" t="n">
-        <v>31200</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>207000</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-42000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>AI 클라우드 수요 폭발 실적 발표에 대한 기대감. 오후 반등 가능성 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['AI', '클라우드', '실적']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>191600</v>
+        <v>15040</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.99%</t>
+          <t>-3.84%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="G21" t="n">
-        <v>88</v>
+        <v>205</v>
       </c>
       <c r="H21" t="n">
-        <v>75.98999999999999</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>197500</v>
+        <v>15640</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2355,10 +2355,10 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>75.92</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>327833000000</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2367,14 +2367,14 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>-405000</v>
+        <v>22000</v>
       </c>
       <c r="S21" t="n">
-        <v>-52000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 증시 하락 및 기관/외인 매도세로 주가 하락 압력을 받으며, 배당금 대비 주가 하락에 대한 불만이 나타남.</t>
+          <t>금호건설, 호남 반도체 부지 100만평 추가 확보 검토 및 삼성전자 신축 공장 수주 소식. 친환경 및 폐기물 처리 사업 관련 성장성 기대.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['우선주', '기관 매도', '미국 증시']</t>
+          <t>['반도체 부지', '신축 공장 수주', '친환경']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,138 +2396,138 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14100</v>
+        <v>258250</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.42%</t>
+          <t>-4.17%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>68</v>
+        <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>47</v>
+        <v>508</v>
       </c>
       <c r="G22" t="n">
-        <v>410</v>
+        <v>1693</v>
       </c>
       <c r="H22" t="n">
-        <v>5.98</v>
+        <v>46.71</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>14600</v>
+        <v>269500</v>
       </c>
       <c r="K22" t="n">
-        <v>14800</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>14950</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>14020</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>6.09</v>
+        <v>46.81</v>
       </c>
       <c r="O22" t="n">
-        <v>71093849200</v>
+        <v>1504840000000</v>
       </c>
       <c r="P22" t="n">
-        <v>30200</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3540</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-297000</v>
+        <v>-1232000</v>
       </c>
       <c r="S22" t="n">
-        <v>-61000</v>
+        <v>-646000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>원전 관련 테마 기대감 속에서 모건 스탠리의 대량 매수 관측. 단기 과열 우려도 있으나, 원전주의 강력한 재료 기반 상승 가능성 언급.</t>
+          <t>반도체 수출 호조에도 불구하고 주가 하락. 네이버 증권 게시판 UI 변경에 대한 불만 다수.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['원전 테마', '모건 스탠리', '수주']</t>
+          <t>['반도체', '수출', '주가']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1784000</v>
+        <v>9280</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.88%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>800</v>
+        <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>472</v>
+        <v>37</v>
       </c>
       <c r="G23" t="n">
-        <v>1148</v>
+        <v>229</v>
       </c>
       <c r="H23" t="n">
-        <v>50.55</v>
+        <v>4.49</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1856000</v>
+        <v>9800</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2539,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>50.67</v>
+        <v>4.42</v>
       </c>
       <c r="O23" t="n">
-        <v>2007266000000</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2551,67 +2551,67 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>-166000</v>
+        <v>-88000</v>
       </c>
       <c r="S23" t="n">
-        <v>-111000</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>AI 클라우드 수요 증가 및 오라클 실적 호조에도 불구하고 주가 하락세. 반도체 수출 증가 언급과 함께 오후 반등 기대.</t>
+          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['AI 클라우드', '반도체 수출', '오후 반등']</t>
+          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>257500</v>
+        <v>191900</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-4.28%</t>
+          <t>-5.47%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>800</v>
+        <v>73</v>
       </c>
       <c r="F24" t="n">
-        <v>504</v>
+        <v>51</v>
       </c>
       <c r="G24" t="n">
-        <v>1738</v>
+        <v>91</v>
       </c>
       <c r="H24" t="n">
-        <v>46.71</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,28 +2619,28 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>269000</v>
+        <v>203000</v>
       </c>
       <c r="K24" t="n">
-        <v>258000</v>
+        <v>195000</v>
       </c>
       <c r="L24" t="n">
-        <v>261000</v>
+        <v>195600</v>
       </c>
       <c r="M24" t="n">
-        <v>257500</v>
+        <v>191000</v>
       </c>
       <c r="N24" t="n">
-        <v>46.81</v>
+        <v>75.92</v>
       </c>
       <c r="O24" t="n">
-        <v>1443597970500</v>
+        <v>337113178950</v>
       </c>
       <c r="P24" t="n">
-        <v>374500</v>
+        <v>243500</v>
       </c>
       <c r="Q24" t="n">
-        <v>72100</v>
+        <v>58600</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -2650,29 +2650,29 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>반도체 수출 역대 최대 기록에도 불구하고 주가 하락. 네이버 증권 게시판 UI 변경에 대한 불만과 함께 정치적 이슈 언급.</t>
+          <t>미국 증시 하락 및 기관/외인 매도세로 주가 하락 압력을 받으며, 배당금 대비 주가 하락에 대한 불만이 나타남.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['반도체 수출', '주가 하락', '게시판 UI']</t>
+          <t>['우선주', '기관 매도', '미국 증시']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12060</v>
+        <v>12120</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-4.51%</t>
+          <t>-6.98%</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2697,10 +2697,10 @@
         <v>59</v>
       </c>
       <c r="F25" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G25" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H25" t="n">
         <v>0.9399999999999999</v>
@@ -2711,31 +2711,31 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>12630</v>
+        <v>13030</v>
       </c>
       <c r="K25" t="n">
-        <v>12520</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>12930</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>12010</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0.14</v>
       </c>
       <c r="O25" t="n">
-        <v>33516494725</v>
+        <v>33724000000</v>
       </c>
       <c r="P25" t="n">
-        <v>20850</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4020</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>-94000</v>
+        <v>-69000</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2771,175 +2771,175 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3605</v>
+        <v>234000</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-6.73%</t>
+          <t>-7.51%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.96</v>
       </c>
       <c r="E26" t="n">
-        <v>44</v>
+        <v>184</v>
       </c>
       <c r="F26" t="n">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="G26" t="n">
-        <v>99</v>
+        <v>659</v>
       </c>
       <c r="H26" t="n">
-        <v>0.73</v>
+        <v>7.58</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>3865</v>
+        <v>253000</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>231000</v>
       </c>
       <c r="N26" t="n">
-        <v>1.54</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>35895000000</v>
+        <v>151179885500</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>426000</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>86100</v>
       </c>
       <c r="R26" t="n">
-        <v>214000</v>
+        <v>-298000</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>기관의 꾸준한 매수에도 불구하고 주가 하락. 공매도에 대한 불만 및 주가 방어 요구.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['공매도', '기관매수', '주가방어']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>232500</v>
+        <v>7600</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-8.10%</t>
+          <t>-8.43%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.96</v>
+        <v>0.12</v>
       </c>
       <c r="E27" t="n">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="F27" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="G27" t="n">
-        <v>586</v>
+        <v>608</v>
       </c>
       <c r="H27" t="n">
-        <v>7.58</v>
+        <v>1.29</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>253000</v>
+        <v>8300</v>
       </c>
       <c r="K27" t="n">
-        <v>241000</v>
+        <v>8400</v>
       </c>
       <c r="L27" t="n">
-        <v>241000</v>
+        <v>8700</v>
       </c>
       <c r="M27" t="n">
-        <v>231000</v>
+        <v>7580</v>
       </c>
       <c r="N27" t="n">
-        <v>8.539999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="O27" t="n">
-        <v>142218631500</v>
+        <v>14613807050</v>
       </c>
       <c r="P27" t="n">
-        <v>426000</v>
+        <v>21500</v>
       </c>
       <c r="Q27" t="n">
-        <v>86100</v>
+        <v>2300</v>
       </c>
       <c r="R27" t="n">
-        <v>-224000</v>
+        <v>-12000</v>
       </c>
       <c r="S27" t="n">
-        <v>-14000</v>
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>한미반도체, 공매도 물량 급증으로 인한 주가 하락세. 기관의 소량 매수세 관찰되나 전반적인 매도 압력 우세.</t>
+          <t>WCLC 9월 14일 미친 데이터 발표 및 기술 수출 기대감, 프로그램 매수 유입.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['공매도', '주가 하락', '기관 매수']</t>
+          <t>['임상시험', '기술수출', '데이터발표']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>187660</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260911_11.xlsx
+++ b/data/trending_integrated_20260911_11.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15400</v>
+        <v>16060</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+27.38%</t>
+          <t>+29.94%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.11</v>
+        <v>-0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>324</v>
+        <v>121</v>
       </c>
       <c r="F2" t="n">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="G2" t="n">
-        <v>745</v>
+        <v>97</v>
       </c>
       <c r="H2" t="n">
-        <v>3.14</v>
+        <v>2.39</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12090</v>
+        <v>12360</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>12800</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>16060</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>12690</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03</v>
+        <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>162760000000</v>
+        <v>206173995605</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>30550</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,20 +626,20 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>중동 전쟁 및 국제 유가 급등에 따른 수혜 기대. 3연상 등 단기 급등에 대한 높은 기대감.</t>
+          <t>젠슨 황 발언에 따른 사이버 보안 섹터 급등. 양자보안 관련주 부각.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['국제유가', '중동전쟁', '급등']</t>
+          <t>['젠슨 황', '사이버 보안', '양자보안']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,86 +648,86 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16060</v>
+        <v>139000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+27.36%</t>
+          <t>+20.14%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.22</v>
+        <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G3" t="n">
-        <v>97</v>
+        <v>180</v>
       </c>
       <c r="H3" t="n">
-        <v>2.39</v>
+        <v>4.32</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>12610</v>
+        <v>115700</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>112100</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>147500</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="N3" t="n">
-        <v>2.61</v>
+        <v>4.58</v>
       </c>
       <c r="O3" t="n">
-        <v>205825000000</v>
+        <v>411650601850</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>196800</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>27750</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>96000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>젠슨 황의 사이버 보안 부문 지목에 따른 보안 섹터 급등. 양자 보안 관련 기대감.</t>
+          <t>애플 관련 호재 및 무라타 제작소 이슈로 인한 급등세. 손바뀜 현상 관찰.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['사이버 보안', '젠슨 황', '양자보안']</t>
+          <t>['애플', '무라타', '급등']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,86 +740,86 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>140700</v>
+        <v>2540</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+21.61%</t>
+          <t>+18.97%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.26</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
-        <v>162</v>
+        <v>67</v>
       </c>
       <c r="H4" t="n">
-        <v>4.32</v>
+        <v>3.83</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>115700</v>
+        <v>2135</v>
       </c>
       <c r="K4" t="n">
-        <v>112100</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>147500</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>112000</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.58</v>
+        <v>3.76</v>
       </c>
       <c r="O4" t="n">
-        <v>405333199100</v>
+        <v>82452000000</v>
       </c>
       <c r="P4" t="n">
-        <v>196800</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>27750</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>52000</v>
+        <v>-1884000</v>
       </c>
       <c r="S4" t="n">
-        <v>96000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>애플 및 무라타 관련 호재로 인한 급등세. 손바뀜 및 단기 급등에 대한 기대감.</t>
+          <t>젠슨 황의 사이버보안 섹터 지목과 함께 양자컴퓨터 보조금 지원 소식 언급. 드림시큐리티의 대장주로서의 부각 및 상승 신호.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['애플', '급등', '손바뀜']</t>
+          <t>['젠슨황', '사이버보안', '양자컴퓨터']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,43 +827,43 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2580</v>
+        <v>7710</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+20.84%</t>
+          <t>+17.35%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.79</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G5" t="n">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="H5" t="n">
-        <v>3.83</v>
+        <v>2.15</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2135</v>
+        <v>6570</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -883,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.76</v>
+        <v>2.94</v>
       </c>
       <c r="O5" t="n">
-        <v>80256000000</v>
+        <v>109090000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -895,14 +895,14 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-1884000</v>
+        <v>141000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>젠슨 황의 사이버보안 섹터 지목과 함께 양자컴퓨터 보조금 지원 소식 언급. 드림시큐리티의 대장주로서의 부각 및 상승 신호.</t>
+          <t>광통신 및 위성네트워크 섹터 내 우리로의 대장주 역할 부각. 양자주로서의 재료 풍부 및 13,000원 이상의 목표가 제시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['젠슨황', '사이버보안', '양자컴퓨터']</t>
+          <t>['광통신', '양자주', '대장주']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,86 +924,86 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8010</v>
+        <v>1929</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+19.55%</t>
+          <t>+9.60%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.79</v>
+        <v>0.32</v>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="F6" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="H6" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6700</v>
+        <v>1760</v>
       </c>
       <c r="K6" t="n">
-        <v>6530</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8370</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6430</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.94</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>102385654175</v>
+        <v>37186000000</v>
       </c>
       <c r="P6" t="n">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1206</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>141000</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>광통신 및 위성네트워크 섹터 내 우리로의 대장주 역할 부각. 양자주로서의 재료 풍부 및 13,000원 이상의 목표가 제시.</t>
+          <t>홍해 관련 지정학적 리스크 부각, 유가 상승 기대감 반영. 장금상선 지분 보유 및 외국인 매수 전환 신호 포착.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '양자주', '대장주']</t>
+          <t>['홍해', '유가', '지정학적 리스크']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,82 +1011,82 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27500</v>
+        <v>7680</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+5.36%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01</v>
+        <v>0.1</v>
       </c>
       <c r="E7" t="n">
-        <v>207</v>
+        <v>103</v>
       </c>
       <c r="F7" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="G7" t="n">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="H7" t="n">
-        <v>0.32</v>
+        <v>11.72</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>26100</v>
+        <v>7100</v>
       </c>
       <c r="K7" t="n">
-        <v>26350</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>30300</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>25400</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.33</v>
+        <v>11.62</v>
       </c>
       <c r="O7" t="n">
-        <v>273569020950</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>39350</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>8200</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>43000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>하락장 속에서 상대적으로 선방하며 자금이 유입되는 모습. '절대반지'라는 별칭과 함께 빠른 시세 상승 기대감.</t>
+          <t>기관 매수세 유입 기대감 속 단기 급등락 전망. 외국인 및 기관 투자자 동향 주시 필요.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['하락장', '자금 유입', '상승 기대감']</t>
+          <t>['주가 전망', '기관 매수', '단타 매매']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51000</v>
+        <v>15350</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+1.19%</t>
+          <t>+5.79%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.09</v>
+        <v>3.11</v>
       </c>
       <c r="E8" t="n">
-        <v>125</v>
+        <v>335</v>
       </c>
       <c r="F8" t="n">
-        <v>75</v>
+        <v>196</v>
       </c>
       <c r="G8" t="n">
-        <v>448</v>
+        <v>833</v>
       </c>
       <c r="H8" t="n">
-        <v>38.78</v>
+        <v>3.14</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>50400</v>
+        <v>14510</v>
       </c>
       <c r="K8" t="n">
-        <v>50500</v>
+        <v>17010</v>
       </c>
       <c r="L8" t="n">
-        <v>51100</v>
+        <v>17310</v>
       </c>
       <c r="M8" t="n">
-        <v>49650</v>
+        <v>15290</v>
       </c>
       <c r="N8" t="n">
-        <v>38.69</v>
+        <v>0.03</v>
       </c>
       <c r="O8" t="n">
-        <v>46068681425</v>
+        <v>164425988085</v>
       </c>
       <c r="P8" t="n">
-        <v>67300</v>
+        <v>36200</v>
       </c>
       <c r="Q8" t="n">
-        <v>23150</v>
+        <v>8920</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>-359000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>사우디아라비아 등에서 약 4.7조원 규모의 대형 수주 공시. 겹호재와 상승 추세 속에서 추가 상승 기대감 형성.</t>
+          <t>중동 지정학적 리스크로 인한 국제유가 폭등. 3연상 목표 기대감 형성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['대형 수주', '공시', '상승 추세']</t>
+          <t>['국제유가', '중동 리스크', '3연상']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1923</v>
+        <v>54000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+1.16%</t>
+          <t>+4.25%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.32</v>
+        <v>-0.44</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="H9" t="n">
-        <v>2.44</v>
+        <v>2.92</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1901</v>
+        <v>51800</v>
       </c>
       <c r="K9" t="n">
-        <v>2050</v>
+        <v>51300</v>
       </c>
       <c r="L9" t="n">
-        <v>2080</v>
+        <v>54500</v>
       </c>
       <c r="M9" t="n">
-        <v>1909</v>
+        <v>51300</v>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>3.36</v>
       </c>
       <c r="O9" t="n">
-        <v>36863613589</v>
+        <v>77693227350</v>
       </c>
       <c r="P9" t="n">
-        <v>4795</v>
+        <v>87700</v>
       </c>
       <c r="Q9" t="n">
-        <v>1524</v>
+        <v>17210</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>116000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>홍해 사태와 유가 상승 전망에 따른 전쟁 테마주 관심 증가. 그러나 명확한 근거 부족.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['홍해', '유가', '전쟁테마주']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53800</v>
+        <v>19720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+1.39%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.44</v>
+        <v>0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="G10" t="n">
-        <v>110</v>
+        <v>383</v>
       </c>
       <c r="H10" t="n">
-        <v>2.92</v>
+        <v>10.65</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>53200</v>
+        <v>19450</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.36</v>
+        <v>10.64</v>
       </c>
       <c r="O10" t="n">
-        <v>74889000000</v>
+        <v>70839000000</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1362,60 +1362,60 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>대차 해지 독려 및 공매도 대응 촉구. 목표가 상향 뉴스와 신규 수주 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['대차해지', '공매도', '목표가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>90400</v>
+        <v>253000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.06</v>
+        <v>-0.96</v>
       </c>
       <c r="E11" t="n">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="F11" t="n">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="G11" t="n">
-        <v>712</v>
+        <v>669</v>
       </c>
       <c r="H11" t="n">
-        <v>23.59</v>
+        <v>7.58</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>89900</v>
+        <v>250500</v>
       </c>
       <c r="K11" t="n">
-        <v>88700</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90400</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>23.65</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>95154336650</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-264000</v>
+        <v>-298000</v>
       </c>
       <c r="S11" t="n">
-        <v>26000</v>
+        <v>-18000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 에너지 투자 협상 마무리 및 원전 사업 수주 기대감. 수주 잔고 증가에 따른 상승 전망.</t>
+          <t>기관의 꾸준한 매수에도 불구하고 주가 하락. 공매도에 대한 불만 및 주가 방어 요구.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전', '수주', '에너지']</t>
+          <t>['공매도', '기관매수', '주가방어']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,130 +1476,130 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3635</v>
+        <v>415500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="E12" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>101</v>
+        <v>207</v>
       </c>
       <c r="H12" t="n">
-        <v>0.73</v>
+        <v>38.02</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3620</v>
+        <v>415500</v>
       </c>
       <c r="K12" t="n">
-        <v>3725</v>
+        <v>407000</v>
       </c>
       <c r="L12" t="n">
-        <v>3915</v>
+        <v>418000</v>
       </c>
       <c r="M12" t="n">
-        <v>3550</v>
+        <v>404000</v>
       </c>
       <c r="N12" t="n">
-        <v>1.54</v>
+        <v>37.82</v>
       </c>
       <c r="O12" t="n">
-        <v>36517568946</v>
+        <v>39574691500</v>
       </c>
       <c r="P12" t="n">
-        <v>4335</v>
+        <v>822000</v>
       </c>
       <c r="Q12" t="n">
-        <v>1246</v>
+        <v>283000</v>
       </c>
       <c r="R12" t="n">
-        <v>64000</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>로봇 사업 확장 및 아틀라스 관절 부품 수주. 유럽 중국차 관세 관련 반사이익 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['로봇', '수주', '관세']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>416500</v>
+        <v>50400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="E13" t="n">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="G13" t="n">
-        <v>201</v>
+        <v>461</v>
       </c>
       <c r="H13" t="n">
-        <v>38.02</v>
+        <v>38.78</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>415500</v>
+        <v>50800</v>
       </c>
       <c r="K13" t="n">
-        <v>407000</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>418000</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>404000</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>37.82</v>
+        <v>38.69</v>
       </c>
       <c r="O13" t="n">
-        <v>37789595250</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>822000</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>283000</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>로봇 사업 확장 및 아틀라스 관절 부품 수주. 유럽 중국차 관세 관련 반사이익 기대.</t>
+          <t>약 4.7조원 규모의 대규모 수주 공시 발표. 사우디 베트남 관련 겹호재 영향.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['로봇', '수주', '관세']</t>
+          <t>['수주 공시', '사우디', '4.7조원']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19620</v>
+        <v>29550</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.01</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="F14" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="G14" t="n">
-        <v>373</v>
+        <v>120</v>
       </c>
       <c r="H14" t="n">
-        <v>10.65</v>
+        <v>25.55</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>19750</v>
+        <v>29800</v>
       </c>
       <c r="K14" t="n">
-        <v>19500</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>19840</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>19060</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>10.64</v>
+        <v>24.99</v>
       </c>
       <c r="O14" t="n">
-        <v>68652679475</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>265000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-69000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대차 해지 독려 및 공매도 대응 촉구. 목표가 상향 뉴스와 신규 수주 기대감.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '목표가']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8850</v>
+        <v>8830</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.34%</t>
+          <t>-1.56%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.03</v>
       </c>
       <c r="E15" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F15" t="n">
         <v>39</v>
       </c>
       <c r="G15" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="H15" t="n">
         <v>27.19</v>
@@ -1806,7 +1806,7 @@
         <v>27.16</v>
       </c>
       <c r="O15" t="n">
-        <v>12080139625</v>
+        <v>12520400490</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1815,10 +1815,10 @@
         <v>8120</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-100000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-78000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14430</v>
+        <v>14360</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.10%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.39</v>
+        <v>-0.11</v>
       </c>
       <c r="E16" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F16" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G16" t="n">
-        <v>186</v>
+        <v>426</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5</v>
+        <v>5.98</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,28 +1883,28 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14740</v>
+        <v>14600</v>
       </c>
       <c r="K16" t="n">
-        <v>14050</v>
+        <v>14800</v>
       </c>
       <c r="L16" t="n">
-        <v>14560</v>
+        <v>14950</v>
       </c>
       <c r="M16" t="n">
-        <v>14030</v>
+        <v>14020</v>
       </c>
       <c r="N16" t="n">
-        <v>2.89</v>
+        <v>6.09</v>
       </c>
       <c r="O16" t="n">
-        <v>39288197395</v>
+        <v>76109009575</v>
       </c>
       <c r="P16" t="n">
-        <v>31500</v>
+        <v>30200</v>
       </c>
       <c r="Q16" t="n">
-        <v>1272</v>
+        <v>3540</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>외국인 매수세 및 프로그램 매수에 따른 상승 기대감 존재. 단기적인 상승 움직임 예측되나, 전반적인 증시 하락 분위기 속에 관망세 짙음.</t>
+          <t>원전 관련 테마 기대감 속에서 모건 스탠리의 대량 매수 관측. 단기 과열 우려도 있으나, 원전주의 강력한 재료 기반 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['외국인', '매수', '움직임']</t>
+          <t>['원전 테마', '모건 스탠리', '수주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,130 +1936,130 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14220</v>
+        <v>89900</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.60%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.11</v>
+        <v>-0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="F17" t="n">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="G17" t="n">
-        <v>418</v>
+        <v>731</v>
       </c>
       <c r="H17" t="n">
-        <v>5.98</v>
+        <v>23.59</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>14600</v>
+        <v>91700</v>
       </c>
       <c r="K17" t="n">
-        <v>14800</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>14950</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>14020</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>6.09</v>
+        <v>23.65</v>
       </c>
       <c r="O17" t="n">
-        <v>72874979345</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>30200</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3540</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-371000</v>
+        <v>-264000</v>
       </c>
       <c r="S17" t="n">
-        <v>-69000</v>
+        <v>26000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>원전 관련 테마 기대감 속에서 모건 스탠리의 대량 매수 관측. 단기 과열 우려도 있으나, 원전주의 강력한 재료 기반 상승 가능성 언급.</t>
+          <t>미국 투자 협상 마무리 및 원전 수주 기대감. 29.7조원 수주잔고 기반 상승 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['원전 테마', '모건 스탠리', '수주']</t>
+          <t>['원전', '수주', '미국 투자']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28750</v>
+        <v>192900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.71%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="F18" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G18" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H18" t="n">
-        <v>51.28</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,28 +2067,28 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>29550</v>
+        <v>197500</v>
       </c>
       <c r="K18" t="n">
-        <v>28650</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>28900</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>28500</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>24.99</v>
+        <v>75.92</v>
       </c>
       <c r="O18" t="n">
-        <v>31937758875</v>
+        <v>345989000000</v>
       </c>
       <c r="P18" t="n">
-        <v>31200</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>미국 증시 하락 및 기관/외인 매도세로 주가 하락 압력을 받으며, 배당금 대비 주가 하락에 대한 불만이 나타남.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['우선주', '기관 매도', '미국 증시']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,99 +2120,99 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7410</v>
+        <v>14330</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>-2.78%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.1</v>
+        <v>-0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="F19" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G19" t="n">
-        <v>294</v>
+        <v>195</v>
       </c>
       <c r="H19" t="n">
-        <v>11.72</v>
+        <v>2.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>7680</v>
+        <v>14740</v>
       </c>
       <c r="K19" t="n">
-        <v>7540</v>
+        <v>14050</v>
       </c>
       <c r="L19" t="n">
-        <v>7660</v>
+        <v>14560</v>
       </c>
       <c r="M19" t="n">
-        <v>7390</v>
+        <v>14030</v>
       </c>
       <c r="N19" t="n">
-        <v>11.62</v>
+        <v>2.89</v>
       </c>
       <c r="O19" t="n">
-        <v>7480398680</v>
+        <v>41324427325</v>
       </c>
       <c r="P19" t="n">
-        <v>8850</v>
+        <v>31500</v>
       </c>
       <c r="Q19" t="n">
-        <v>4220</v>
+        <v>1272</v>
       </c>
       <c r="R19" t="n">
-        <v>43000</v>
+        <v>-128000</v>
       </c>
       <c r="S19" t="n">
-        <v>-2000</v>
+        <v>-6000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>기관 매수세 및 주가 반등 기대감과 공매도 우려.</t>
+          <t>외국인 매수세 및 프로그램 매수에 따른 상승 기대감 존재. 단기적인 상승 움직임 예측되나, 전반적인 증시 하락 분위기 속에 관망세 짙음.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['기관매매', '공매도', '주가전망']</t>
+          <t>['외국인', '매수', '움직임']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1787000</v>
+        <v>1792000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.72%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,10 +2237,10 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G20" t="n">
-        <v>1136</v>
+        <v>1181</v>
       </c>
       <c r="H20" t="n">
         <v>50.55</v>
@@ -2266,7 +2266,7 @@
         <v>50.67</v>
       </c>
       <c r="O20" t="n">
-        <v>2085672000000</v>
+        <v>2214296000000</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2275,14 +2275,14 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>-249000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-102000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>AI 클라우드 수요 폭발 실적 발표에 대한 기대감. 오후 반등 가능성 언급.</t>
+          <t>장 초반 하락세이나 오후 반등 기대감 존재. 반도체 수출 지표와 달리 주가 부진.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['AI', '클라우드', '실적']</t>
+          <t>['반도체 수출', '주가 부진', '오후 반등']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F21" t="n">
         <v>33</v>
       </c>
       <c r="G21" t="n">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>258250</v>
+        <v>258000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.17%</t>
+          <t>-4.09%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2424,7 +2424,7 @@
         <v>508</v>
       </c>
       <c r="G22" t="n">
-        <v>1693</v>
+        <v>1657</v>
       </c>
       <c r="H22" t="n">
         <v>46.71</v>
@@ -2435,28 +2435,28 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>269500</v>
+        <v>269000</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>258000</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>257500</v>
       </c>
       <c r="N22" t="n">
         <v>46.81</v>
       </c>
       <c r="O22" t="n">
-        <v>1504840000000</v>
+        <v>1588512861500</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>72100</v>
       </c>
       <c r="R22" t="n">
         <v>-1232000</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>반도체 수출 호조에도 불구하고 주가 하락. 네이버 증권 게시판 UI 변경에 대한 불만 다수.</t>
+          <t>반도체 수출 호조에도 불구하고 주가 하락세 지속. 네이버 증권 UI 변경에 대한 불만 제기.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['반도체', '수출', '주가']</t>
+          <t>['반도체 수출', '주가 하락', '네이버 증권']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2516,7 +2516,7 @@
         <v>37</v>
       </c>
       <c r="G23" t="n">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="H23" t="n">
         <v>4.49</v>
@@ -2587,70 +2587,70 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>191900</v>
+        <v>12260</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-5.47%</t>
+          <t>-5.91%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="E24" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="F24" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="G24" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="H24" t="n">
-        <v>75.98999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>203000</v>
+        <v>13030</v>
       </c>
       <c r="K24" t="n">
-        <v>195000</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>195600</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>191000</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>75.92</v>
+        <v>0.14</v>
       </c>
       <c r="O24" t="n">
-        <v>337113178950</v>
+        <v>34855000000</v>
       </c>
       <c r="P24" t="n">
-        <v>243500</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>58600</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>-69000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>미국 증시 하락 및 기관/외인 매도세로 주가 하락 압력을 받으며, 배당금 대비 주가 하락에 대한 불만이 나타남.</t>
+          <t>원전 테마주로서의 삼미금속 언급. 한전기술 등 타 원전주들의 급등 속 상대적 부진 및 거래량 부족에 대한 지적.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['우선주', '기관 매도', '미국 증시']</t>
+          <t>['원전', '테마주', '거래량']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,38 +2672,38 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12120</v>
+        <v>3590</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-6.98%</t>
+          <t>-7.12%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F25" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G25" t="n">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>13030</v>
+        <v>3865</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2723,10 +2723,10 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0.14</v>
+        <v>1.54</v>
       </c>
       <c r="O25" t="n">
-        <v>33724000000</v>
+        <v>37157000000</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2735,14 +2735,14 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>-69000</v>
+        <v>64000</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>원전 테마주로서의 삼미금속 언급. 한전기술 등 타 원전주들의 급등 속 상대적 부진 및 거래량 부족에 대한 지적.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,11 +2751,11 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['원전', '테마주', '거래량']</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,90 +2764,90 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>234000</v>
+        <v>7650</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-7.51%</t>
+          <t>-7.83%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.96</v>
+        <v>0.12</v>
       </c>
       <c r="E26" t="n">
-        <v>184</v>
+        <v>142</v>
       </c>
       <c r="F26" t="n">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="G26" t="n">
-        <v>659</v>
+        <v>632</v>
       </c>
       <c r="H26" t="n">
-        <v>7.58</v>
+        <v>1.29</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>253000</v>
+        <v>8300</v>
       </c>
       <c r="K26" t="n">
-        <v>241000</v>
+        <v>8400</v>
       </c>
       <c r="L26" t="n">
-        <v>241000</v>
+        <v>8700</v>
       </c>
       <c r="M26" t="n">
-        <v>231000</v>
+        <v>7580</v>
       </c>
       <c r="N26" t="n">
-        <v>8.539999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="O26" t="n">
-        <v>151179885500</v>
+        <v>14971975405</v>
       </c>
       <c r="P26" t="n">
-        <v>426000</v>
+        <v>21500</v>
       </c>
       <c r="Q26" t="n">
-        <v>86100</v>
+        <v>2300</v>
       </c>
       <c r="R26" t="n">
-        <v>-298000</v>
+        <v>-12000</v>
       </c>
       <c r="S26" t="n">
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>기관의 꾸준한 매수에도 불구하고 주가 하락. 공매도에 대한 불만 및 주가 방어 요구.</t>
+          <t>9월 14일 WCLC 학회에서의 데이터 발표 기대감. 기술 수출 관련 가능성 제기.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['공매도', '기관매수', '주가방어']</t>
+          <t>['임상 데이터', 'WCLC', '기술 수출']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,38 +2856,38 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7600</v>
+        <v>27700</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-8.43%</t>
+          <t>-8.58%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="E27" t="n">
-        <v>133</v>
+        <v>214</v>
       </c>
       <c r="F27" t="n">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="G27" t="n">
-        <v>608</v>
+        <v>334</v>
       </c>
       <c r="H27" t="n">
-        <v>1.29</v>
+        <v>0.32</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2895,51 +2895,51 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>8300</v>
+        <v>30300</v>
       </c>
       <c r="K27" t="n">
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>7580</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.17</v>
+        <v>0.33</v>
       </c>
       <c r="O27" t="n">
-        <v>14613807050</v>
+        <v>285026000000</v>
       </c>
       <c r="P27" t="n">
-        <v>21500</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>-12000</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>WCLC 9월 14일 미친 데이터 발표 및 기술 수출 기대감, 프로그램 매수 유입.</t>
+          <t>하락장 속 신규주로서의 매력 부각, 외인 수급 유입 신호 감지. 3일간 조정 후 반등 기대.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['임상시험', '기술수출', '데이터발표']</t>
+          <t>['신규주', '외인 수급', '하락장']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>386380</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260911_11.xlsx
+++ b/data/trending_integrated_20260911_11.xlsx
@@ -571,20 +571,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+29.94%</t>
+          <t>+27.36%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F2" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G2" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H2" t="n">
         <v>2.39</v>
@@ -595,38 +595,38 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12360</v>
+        <v>12610</v>
       </c>
       <c r="K2" t="n">
-        <v>12800</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>16060</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>12690</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>206173995605</v>
+        <v>206415000000</v>
       </c>
       <c r="P2" t="n">
-        <v>30550</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-71000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>젠슨 황 발언에 따른 사이버 보안 섹터 급등. 양자보안 관련주 부각.</t>
+          <t>젠슨 황의 사이버 보안 시장 강조 발언으로 인한 급등. 양자 보안 테마 부각 및 2연상 기대감 형성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['젠슨 황', '사이버 보안', '양자보안']</t>
+          <t>['젠슨 황', '사이버 보안', '양자 보안']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>139000</v>
+        <v>15360</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+20.14%</t>
+          <t>+27.05%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.26</v>
+        <v>3.11</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>332</v>
       </c>
       <c r="F3" t="n">
-        <v>77</v>
+        <v>197</v>
       </c>
       <c r="G3" t="n">
-        <v>180</v>
+        <v>828</v>
       </c>
       <c r="H3" t="n">
-        <v>4.32</v>
+        <v>3.14</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>115700</v>
+        <v>12090</v>
       </c>
       <c r="K3" t="n">
-        <v>112100</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>147500</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>112000</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.58</v>
+        <v>0.03</v>
       </c>
       <c r="O3" t="n">
-        <v>411650601850</v>
+        <v>165951000000</v>
       </c>
       <c r="P3" t="n">
-        <v>196800</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>27750</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>52000</v>
+        <v>-359000</v>
       </c>
       <c r="S3" t="n">
-        <v>96000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>애플 관련 호재 및 무라타 제작소 이슈로 인한 급등세. 손바뀜 현상 관찰.</t>
+          <t>중동 전쟁 및 유가 급등에 따른 수혜 기대감. 3연상 및 100달러 돌파 WTI 관련 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['애플', '무라타', '급등']</t>
+          <t>['유가 급등', '중동 전쟁', 'WTI']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2540</v>
+        <v>2550</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+18.97%</t>
+          <t>+19.44%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H4" t="n">
         <v>3.83</v>
@@ -794,7 +794,7 @@
         <v>3.76</v>
       </c>
       <c r="O4" t="n">
-        <v>82452000000</v>
+        <v>84712000000</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -839,152 +839,152 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7710</v>
+        <v>138100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+17.35%</t>
+          <t>+19.36%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.79</v>
+        <v>-0.26</v>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="G5" t="n">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="H5" t="n">
-        <v>2.15</v>
+        <v>4.32</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6570</v>
+        <v>115700</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>112100</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>147500</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="N5" t="n">
-        <v>2.94</v>
+        <v>4.58</v>
       </c>
       <c r="O5" t="n">
-        <v>109090000000</v>
+        <v>417243647350</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>196800</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>27750</v>
       </c>
       <c r="R5" t="n">
-        <v>141000</v>
+        <v>52000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>96000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광통신 및 위성네트워크 섹터 내 우리로의 대장주 역할 부각. 양자주로서의 재료 풍부 및 13,000원 이상의 목표가 제시.</t>
+          <t>애플 관련주로 부각되며 급등세 연출. 손바뀜 및 단기적 시세 분출 가능성 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '양자주', '대장주']</t>
+          <t>['애플', '손바뀜', '단기 급등']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1929</v>
+        <v>7740</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+9.60%</t>
+          <t>+15.52%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.32</v>
+        <v>-0.79</v>
       </c>
       <c r="E6" t="n">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G6" t="n">
-        <v>151</v>
+        <v>209</v>
       </c>
       <c r="H6" t="n">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1760</v>
+        <v>6700</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>6530</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>8370</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>6430</v>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>2.94</v>
       </c>
       <c r="O6" t="n">
-        <v>37186000000</v>
+        <v>114032236005</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1206</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>홍해 관련 지정학적 리스크 부각, 유가 상승 기대감 반영. 장금상선 지분 보유 및 외국인 매수 전환 신호 포착.</t>
+          <t>광통신 및 위성네트워크 섹터 내 우리로의 대장주 역할 부각. 양자주로서의 재료 풍부 및 13,000원 이상의 목표가 제시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['홍해', '유가', '지정학적 리스크']</t>
+          <t>['광통신', '양자주', '대장주']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,51 +1011,51 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7680</v>
+        <v>8300</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+11.86%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>103</v>
+        <v>150</v>
       </c>
       <c r="F7" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
-        <v>301</v>
+        <v>659</v>
       </c>
       <c r="H7" t="n">
-        <v>11.72</v>
+        <v>1.29</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7100</v>
+        <v>7420</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1067,7 +1067,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>11.62</v>
+        <v>1.17</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1079,27 +1079,27 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>43000</v>
+        <v>-12000</v>
       </c>
       <c r="S7" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>기관 매수세 유입 기대감 속 단기 급등락 전망. 외국인 및 기관 투자자 동향 주시 필요.</t>
+          <t>핵심 기술 발표 임박 및 임상 시험 관련 기대감 형성. 일부 투자자들의 긍정적 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가 전망', '기관 매수', '단타 매매']</t>
+          <t>['임상', '발표', '기술수출']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15350</v>
+        <v>9980</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.79%</t>
+          <t>+7.54%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>335</v>
+        <v>62</v>
       </c>
       <c r="F8" t="n">
-        <v>196</v>
+        <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>833</v>
+        <v>250</v>
       </c>
       <c r="H8" t="n">
-        <v>3.14</v>
+        <v>4.49</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,183 +1147,183 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14510</v>
+        <v>9280</v>
       </c>
       <c r="K8" t="n">
-        <v>17010</v>
+        <v>10030</v>
       </c>
       <c r="L8" t="n">
-        <v>17310</v>
+        <v>10880</v>
       </c>
       <c r="M8" t="n">
-        <v>15290</v>
+        <v>9800</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03</v>
+        <v>4.42</v>
       </c>
       <c r="O8" t="n">
-        <v>164425988085</v>
+        <v>20037089230</v>
       </c>
       <c r="P8" t="n">
-        <v>36200</v>
+        <v>15640</v>
       </c>
       <c r="Q8" t="n">
-        <v>8920</v>
+        <v>5470</v>
       </c>
       <c r="R8" t="n">
-        <v>-359000</v>
+        <v>-88000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>중동 지정학적 리스크로 인한 국제유가 폭등. 3연상 목표 기대감 형성.</t>
+          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['국제유가', '중동 리스크', '3연상']</t>
+          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54000</v>
+        <v>27400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+4.25%</t>
+          <t>+4.98%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.44</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>62</v>
+        <v>217</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="G9" t="n">
-        <v>123</v>
+        <v>352</v>
       </c>
       <c r="H9" t="n">
-        <v>2.92</v>
+        <v>0.32</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>51800</v>
+        <v>26100</v>
       </c>
       <c r="K9" t="n">
-        <v>51300</v>
+        <v>26350</v>
       </c>
       <c r="L9" t="n">
-        <v>54500</v>
+        <v>30300</v>
       </c>
       <c r="M9" t="n">
-        <v>51300</v>
+        <v>25400</v>
       </c>
       <c r="N9" t="n">
-        <v>3.36</v>
+        <v>0.33</v>
       </c>
       <c r="O9" t="n">
-        <v>77693227350</v>
+        <v>289258559675</v>
       </c>
       <c r="P9" t="n">
-        <v>87700</v>
+        <v>39350</v>
       </c>
       <c r="Q9" t="n">
-        <v>17210</v>
+        <v>8200</v>
       </c>
       <c r="R9" t="n">
-        <v>116000</v>
+        <v>7000</v>
       </c>
       <c r="S9" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>하락장 속에서 외인 매수세 유입 관찰. 신규주로서 단기 급등 기대감 형성.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['외인 매수', '신규주', '단기 급등']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19720</v>
+        <v>1929</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+1.39%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.01</v>
+        <v>0.32</v>
       </c>
       <c r="E10" t="n">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="F10" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="G10" t="n">
-        <v>383</v>
+        <v>170</v>
       </c>
       <c r="H10" t="n">
-        <v>10.65</v>
+        <v>2.44</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,28 +1331,28 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>19450</v>
+        <v>1901</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2050</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2080</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1909</v>
       </c>
       <c r="N10" t="n">
-        <v>10.64</v>
+        <v>2.12</v>
       </c>
       <c r="O10" t="n">
-        <v>70839000000</v>
+        <v>37463516792</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4795</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1524</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1362,20 +1362,20 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대차 해지 독려 및 공매도 대응 촉구. 목표가 상향 뉴스와 신규 수주 기대감.</t>
+          <t>유가 상승 및 전쟁 테마주로 부각되며 단기적 상승 기대감 형성. 다만, 차익 실현 매물 출회 및 프로그램 매도세 관찰.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '목표가']</t>
+          <t>['유가', '전쟁 테마주', '프로그램 매매']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
@@ -1406,13 +1406,13 @@
         <v>-0.96</v>
       </c>
       <c r="E11" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F11" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G11" t="n">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="H11" t="n">
         <v>7.58</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>415500</v>
+        <v>50900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="E12" t="n">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="G12" t="n">
-        <v>207</v>
+        <v>496</v>
       </c>
       <c r="H12" t="n">
-        <v>38.02</v>
+        <v>38.78</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>415500</v>
+        <v>50400</v>
       </c>
       <c r="K12" t="n">
-        <v>407000</v>
+        <v>50500</v>
       </c>
       <c r="L12" t="n">
-        <v>418000</v>
+        <v>51200</v>
       </c>
       <c r="M12" t="n">
-        <v>404000</v>
+        <v>49650</v>
       </c>
       <c r="N12" t="n">
-        <v>37.82</v>
+        <v>38.69</v>
       </c>
       <c r="O12" t="n">
-        <v>39574691500</v>
+        <v>49723915825</v>
       </c>
       <c r="P12" t="n">
-        <v>822000</v>
+        <v>67300</v>
       </c>
       <c r="Q12" t="n">
-        <v>283000</v>
+        <v>23150</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-134000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>로봇 사업 확장 및 아틀라스 관절 부품 수주. 유럽 중국차 관세 관련 반사이익 기대.</t>
+          <t>약 4.7조원 규모의 대규모 수주 공시 확인. 사우디 및 베트남 관련 복합 호재 기대감 형성.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['로봇', '수주', '관세']</t>
+          <t>['수주', '공시', '호재']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50400</v>
+        <v>53600</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>+0.75%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.09</v>
+        <v>-0.44</v>
       </c>
       <c r="E13" t="n">
-        <v>128</v>
+        <v>62</v>
       </c>
       <c r="F13" t="n">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G13" t="n">
-        <v>461</v>
+        <v>123</v>
       </c>
       <c r="H13" t="n">
-        <v>38.78</v>
+        <v>2.92</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>50800</v>
+        <v>53200</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1619,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>38.69</v>
+        <v>3.36</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>79770000000</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1631,67 +1631,67 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>116000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 대규모 수주 공시 발표. 사우디 베트남 관련 겹호재 영향.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수주 공시', '사우디', '4.7조원']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29550</v>
+        <v>415000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="E14" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="F14" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="H14" t="n">
-        <v>25.55</v>
+        <v>38.02</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,91 +1699,91 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>29800</v>
+        <v>415500</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>407000</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>418000</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>404000</v>
       </c>
       <c r="N14" t="n">
-        <v>24.99</v>
+        <v>37.82</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>40522524500</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>822000</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>283000</v>
       </c>
       <c r="R14" t="n">
-        <v>265000</v>
+        <v>13000</v>
       </c>
       <c r="S14" t="n">
-        <v>-69000</v>
+        <v>1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>로봇 사업 확장 및 신기술 공개로 인한 수주 기대감. 유럽 중국차 관세 관련 호재 및 저평가 논의.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['로봇 사업', '수주', '관세']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8830</v>
+        <v>19710</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="F15" t="n">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="G15" t="n">
-        <v>195</v>
+        <v>395</v>
       </c>
       <c r="H15" t="n">
-        <v>27.19</v>
+        <v>10.65</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,60 +1791,60 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8970</v>
+        <v>19750</v>
       </c>
       <c r="K15" t="n">
-        <v>8780</v>
+        <v>19500</v>
       </c>
       <c r="L15" t="n">
-        <v>8880</v>
+        <v>19840</v>
       </c>
       <c r="M15" t="n">
-        <v>8680</v>
+        <v>19060</v>
       </c>
       <c r="N15" t="n">
-        <v>27.16</v>
+        <v>10.64</v>
       </c>
       <c r="O15" t="n">
-        <v>12520400490</v>
+        <v>74714791305</v>
       </c>
       <c r="P15" t="n">
-        <v>17950</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>8120</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>-100000</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-78000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 강한 불만과 함께 회사의 실적 부진 및 저평가에 대한 부정적인 인식이 지배적임.</t>
+          <t>대차 해지 및 공매도 관련 논의 활발. 목표가 상향 뉴스 및 대규모 수주 기대감 형성.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['저평가', '실적 부진', '금리 인상']</t>
+          <t>['대차 해지', '공매도', '목표가 상향']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14360</v>
+        <v>14480</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.11</v>
       </c>
       <c r="E16" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F16" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G16" t="n">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="H16" t="n">
         <v>5.98</v>
@@ -1898,7 +1898,7 @@
         <v>6.09</v>
       </c>
       <c r="O16" t="n">
-        <v>76109009575</v>
+        <v>80126434970</v>
       </c>
       <c r="P16" t="n">
         <v>30200</v>
@@ -1907,23 +1907,23 @@
         <v>3540</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>-371000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-69000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>원전 관련 테마 기대감 속에서 모건 스탠리의 대량 매수 관측. 단기 과열 우려도 있으나, 원전주의 강력한 재료 기반 상승 가능성 언급.</t>
+          <t>원전 관련주로 언급되며 상승 기대감 형성. 특정 세력의 개입 및 단기 과열 가능성 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전 테마', '모건 스탠리', '수주']</t>
+          <t>['원전', '단기 과열', '외인 매매']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>89900</v>
+        <v>29550</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.06</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>173</v>
+        <v>47</v>
       </c>
       <c r="F17" t="n">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="G17" t="n">
-        <v>731</v>
+        <v>121</v>
       </c>
       <c r="H17" t="n">
-        <v>23.59</v>
+        <v>25.55</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>91700</v>
+        <v>29800</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1987,7 +1987,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>23.65</v>
+        <v>24.99</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1999,96 +1999,96 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-264000</v>
+        <v>265000</v>
       </c>
       <c r="S17" t="n">
-        <v>26000</v>
+        <v>-69000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 투자 협상 마무리 및 원전 수주 기대감. 29.7조원 수주잔고 기반 상승 전망.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['원전', '수주', '미국 투자']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>192900</v>
+        <v>3570</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="G18" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="H18" t="n">
-        <v>75.98999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>197500</v>
+        <v>3620</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>3725</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3915</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3550</v>
       </c>
       <c r="N18" t="n">
-        <v>75.92</v>
+        <v>1.54</v>
       </c>
       <c r="O18" t="n">
-        <v>345989000000</v>
+        <v>37804221054</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>4335</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 증시 하락 및 기관/외인 매도세로 주가 하락 압력을 받으며, 배당금 대비 주가 하락에 대한 불만이 나타남.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['우선주', '기관 매도', '미국 증시']</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14330</v>
+        <v>8810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.78%</t>
+          <t>-1.78%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.39</v>
+        <v>0.03</v>
       </c>
       <c r="E19" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="F19" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5</v>
+        <v>27.19</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>14740</v>
+        <v>8970</v>
       </c>
       <c r="K19" t="n">
-        <v>14050</v>
+        <v>8780</v>
       </c>
       <c r="L19" t="n">
-        <v>14560</v>
+        <v>8880</v>
       </c>
       <c r="M19" t="n">
-        <v>14030</v>
+        <v>8680</v>
       </c>
       <c r="N19" t="n">
-        <v>2.89</v>
+        <v>27.16</v>
       </c>
       <c r="O19" t="n">
-        <v>41324427325</v>
+        <v>12941152720</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>17950</v>
       </c>
       <c r="Q19" t="n">
-        <v>1272</v>
+        <v>8120</v>
       </c>
       <c r="R19" t="n">
-        <v>-128000</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>외국인 매수세 및 프로그램 매수에 따른 상승 기대감 존재. 단기적인 상승 움직임 예측되나, 전반적인 증시 하락 분위기 속에 관망세 짙음.</t>
+          <t>주가 상승에 대한 강한 불만과 함께 회사의 실적 부진 및 저평가에 대한 부정적인 인식이 지배적임.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['외국인', '매수', '움직임']</t>
+          <t>['저평가', '실적 부진', '금리 인상']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1792000</v>
+        <v>89900</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="E20" t="n">
-        <v>800</v>
+        <v>177</v>
       </c>
       <c r="F20" t="n">
-        <v>464</v>
+        <v>108</v>
       </c>
       <c r="G20" t="n">
-        <v>1181</v>
+        <v>733</v>
       </c>
       <c r="H20" t="n">
-        <v>50.55</v>
+        <v>23.59</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1856000</v>
+        <v>91700</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2263,10 +2263,10 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>50.67</v>
+        <v>23.65</v>
       </c>
       <c r="O20" t="n">
-        <v>2214296000000</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2275,27 +2275,27 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-249000</v>
+        <v>-264000</v>
       </c>
       <c r="S20" t="n">
-        <v>-102000</v>
+        <v>26000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>장 초반 하락세이나 오후 반등 기대감 존재. 반도체 수출 지표와 달리 주가 부진.</t>
+          <t>미국 투자 협상 마무리 및 원전 수주 기대감. 29.7조원 수주잔고 기반 상승 전망.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['반도체 수출', '주가 부진', '오후 반등']</t>
+          <t>['원전', '수주', '미국 투자']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15040</v>
+        <v>192500</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.84%</t>
+          <t>-2.53%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F21" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G21" t="n">
-        <v>213</v>
+        <v>121</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>15640</v>
+        <v>197500</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2355,10 +2355,10 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>75.92</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>354454000000</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2367,14 +2367,14 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>22000</v>
+        <v>-852000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-123000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>금호건설, 호남 반도체 부지 100만평 추가 확보 검토 및 삼성전자 신축 공장 수주 소식. 친환경 및 폐기물 처리 사업 관련 성장성 기대.</t>
+          <t>미국 증시 하락 및 기관/외인 매도세로 주가 하락 압력을 받으며, 배당금 대비 주가 하락에 대한 불만이 나타남.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['반도체 부지', '신축 공장 수주', '친환경']</t>
+          <t>['우선주', '기관 매도', '미국 증시']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>258000</v>
+        <v>7420</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.09%</t>
+          <t>-3.39%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>800</v>
+        <v>104</v>
       </c>
       <c r="F22" t="n">
-        <v>508</v>
+        <v>54</v>
       </c>
       <c r="G22" t="n">
-        <v>1657</v>
+        <v>316</v>
       </c>
       <c r="H22" t="n">
-        <v>46.71</v>
+        <v>11.72</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,38 +2435,38 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>269000</v>
+        <v>7680</v>
       </c>
       <c r="K22" t="n">
-        <v>258000</v>
+        <v>7540</v>
       </c>
       <c r="L22" t="n">
-        <v>261000</v>
+        <v>7660</v>
       </c>
       <c r="M22" t="n">
-        <v>257500</v>
+        <v>7390</v>
       </c>
       <c r="N22" t="n">
-        <v>46.81</v>
+        <v>11.62</v>
       </c>
       <c r="O22" t="n">
-        <v>1588512861500</v>
+        <v>7854366540</v>
       </c>
       <c r="P22" t="n">
-        <v>374500</v>
+        <v>8850</v>
       </c>
       <c r="Q22" t="n">
-        <v>72100</v>
+        <v>4220</v>
       </c>
       <c r="R22" t="n">
-        <v>-1232000</v>
+        <v>43000</v>
       </c>
       <c r="S22" t="n">
-        <v>-646000</v>
+        <v>-2000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>반도체 수출 호조에도 불구하고 주가 하락세 지속. 네이버 증권 UI 변경에 대한 불만 제기.</t>
+          <t>주가 관련 다양한 추측성 언급 및 단기 매매 전략 논의. 뚜렷한 근거 기반 정보 부족.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['반도체 수출', '주가 하락', '네이버 증권']</t>
+          <t>['주가', '매매', '전략']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,138 +2488,138 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9280</v>
+        <v>1785000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-3.67%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="E23" t="n">
-        <v>58</v>
+        <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>37</v>
+        <v>463</v>
       </c>
       <c r="G23" t="n">
-        <v>238</v>
+        <v>1181</v>
       </c>
       <c r="H23" t="n">
-        <v>4.49</v>
+        <v>50.55</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>9800</v>
+        <v>1853000</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1773000</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1795000</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1768000</v>
       </c>
       <c r="N23" t="n">
-        <v>4.42</v>
+        <v>50.67</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2284635417000</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2987000</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>305500</v>
       </c>
       <c r="R23" t="n">
-        <v>-88000</v>
+        <v>-249000</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-102000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
+          <t>AI 클라우드 수요 증가 관련 뉴스 일부 확인. 시장 전반의 하락세 속에서 일부 반등 기대감 존재.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
+          <t>['AI', '실적', '하락세']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12260</v>
+        <v>15040</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-5.91%</t>
+          <t>-3.84%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F24" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>217</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>13030</v>
+        <v>15640</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2631,10 +2631,10 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>34855000000</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2643,14 +2643,14 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>-69000</v>
+        <v>22000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>원전 테마주로서의 삼미금속 언급. 한전기술 등 타 원전주들의 급등 속 상대적 부진 및 거래량 부족에 대한 지적.</t>
+          <t>금호건설, 호남 반도체 부지 100만평 추가 확보 검토 및 삼성전자 신축 공장 수주 소식. 친환경 및 폐기물 처리 사업 관련 성장성 기대.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['원전', '테마주', '거래량']</t>
+          <t>['반도체 부지', '신축 공장 수주', '친환경']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,130 +2672,130 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3590</v>
+        <v>257750</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-7.12%</t>
+          <t>-4.18%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="E25" t="n">
-        <v>47</v>
+        <v>800</v>
       </c>
       <c r="F25" t="n">
-        <v>30</v>
+        <v>508</v>
       </c>
       <c r="G25" t="n">
-        <v>99</v>
+        <v>1640</v>
       </c>
       <c r="H25" t="n">
-        <v>0.73</v>
+        <v>46.71</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>3865</v>
+        <v>269000</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>258000</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>257500</v>
       </c>
       <c r="N25" t="n">
-        <v>1.54</v>
+        <v>46.81</v>
       </c>
       <c r="O25" t="n">
-        <v>37157000000</v>
+        <v>1694276205500</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>72100</v>
       </c>
       <c r="R25" t="n">
-        <v>64000</v>
+        <v>-1232000</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>-646000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>반도체 수출 역대 최대 기록에도 불구하고 주가 하락. 개인 투자자들의 완전 승리 및 외인 매수세 관찰.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['반도체 수출', '영업이익', '외인 매수']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7650</v>
+        <v>14330</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-7.83%</t>
+          <t>-4.21%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.12</v>
+        <v>-0.39</v>
       </c>
       <c r="E26" t="n">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="F26" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="G26" t="n">
-        <v>632</v>
+        <v>202</v>
       </c>
       <c r="H26" t="n">
-        <v>1.29</v>
+        <v>2.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2803,51 +2803,51 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>8300</v>
+        <v>14960</v>
       </c>
       <c r="K26" t="n">
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>7580</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.17</v>
+        <v>2.89</v>
       </c>
       <c r="O26" t="n">
-        <v>14971975405</v>
+        <v>42540000000</v>
       </c>
       <c r="P26" t="n">
-        <v>21500</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>-12000</v>
+        <v>-128000</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>9월 14일 WCLC 학회에서의 데이터 발표 기대감. 기술 수출 관련 가능성 제기.</t>
+          <t>광통신 섹터의 상승 기대감 속에서 외국인 매수세 유입. 2만원 목표가 제시 및 장기 보유 관점.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['임상 데이터', 'WCLC', '기술 수출']</t>
+          <t>['광통신', '외국인 매수', '장기 보유']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,38 +2856,38 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27700</v>
+        <v>12310</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-8.58%</t>
+          <t>-5.53%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.01</v>
+        <v>0.8</v>
       </c>
       <c r="E27" t="n">
-        <v>214</v>
+        <v>58</v>
       </c>
       <c r="F27" t="n">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="G27" t="n">
-        <v>334</v>
+        <v>60</v>
       </c>
       <c r="H27" t="n">
-        <v>0.32</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>30300</v>
+        <v>13030</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="O27" t="n">
-        <v>285026000000</v>
+        <v>35632000000</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2919,36 +2919,36 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>-69000</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>하락장 속 신규주로서의 매력 부각, 외인 수급 유입 신호 감지. 3일간 조정 후 반등 기대.</t>
+          <t>원전 테마주로서의 삼미금속 언급. 한전기술 등 타 원전주들의 급등 속 상대적 부진 및 거래량 부족에 대한 지적.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['신규주', '외인 수급', '하락장']</t>
+          <t>['원전', '테마주', '거래량']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>012210</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260911_11.xlsx
+++ b/data/trending_integrated_20260911_11.xlsx
@@ -578,13 +578,13 @@
         <v>-0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F2" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H2" t="n">
         <v>2.39</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>206415000000</v>
+        <v>206661000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>젠슨 황의 사이버 보안 시장 강조 발언으로 인한 급등. 양자 보안 테마 부각 및 2연상 기대감 형성.</t>
+          <t>젠슨 황의 AI 다음 핵심 시장으로 사이버 보안 부문 지목에 따른 엑스게이트의 급등 기대. 양자보안 관련 내용 포함.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['젠슨 황', '사이버 보안', '양자 보안']</t>
+          <t>['사이버 보안', '젠슨 황', '양자보안']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15360</v>
+        <v>138300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+27.05%</t>
+          <t>+19.53%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.11</v>
+        <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>332</v>
+        <v>105</v>
       </c>
       <c r="F3" t="n">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
-        <v>828</v>
+        <v>194</v>
       </c>
       <c r="H3" t="n">
-        <v>3.14</v>
+        <v>4.32</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>12090</v>
+        <v>115700</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>112100</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>147500</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03</v>
+        <v>4.58</v>
       </c>
       <c r="O3" t="n">
-        <v>165951000000</v>
+        <v>421628622150</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>196800</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>27750</v>
       </c>
       <c r="R3" t="n">
-        <v>-359000</v>
+        <v>52000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>96000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>중동 전쟁 및 유가 급등에 따른 수혜 기대감. 3연상 및 100달러 돌파 WTI 관련 언급.</t>
+          <t>애플 관련주로 부각되며 급등세 연출. 손바뀜 및 단기적 시세 분출 가능성 제기.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['유가 급등', '중동 전쟁', 'WTI']</t>
+          <t>['애플', '손바뀜', '단기 급등']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2550</v>
+        <v>2530</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+19.44%</t>
+          <t>+19.06%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,7 +765,7 @@
         <v>65</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
         <v>72</v>
@@ -779,28 +779,28 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2135</v>
+        <v>2125</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2230</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2692</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2170</v>
       </c>
       <c r="N4" t="n">
         <v>3.76</v>
       </c>
       <c r="O4" t="n">
-        <v>84712000000</v>
+        <v>86322008419</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4810</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="R4" t="n">
         <v>-1884000</v>
@@ -839,123 +839,123 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>138100</v>
+        <v>7590</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+19.36%</t>
+          <t>+13.28%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.26</v>
+        <v>-0.79</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="F5" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>181</v>
+        <v>223</v>
       </c>
       <c r="H5" t="n">
-        <v>4.32</v>
+        <v>2.15</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>115700</v>
+        <v>6700</v>
       </c>
       <c r="K5" t="n">
-        <v>112100</v>
+        <v>6530</v>
       </c>
       <c r="L5" t="n">
-        <v>147500</v>
+        <v>8370</v>
       </c>
       <c r="M5" t="n">
-        <v>112000</v>
+        <v>6430</v>
       </c>
       <c r="N5" t="n">
-        <v>4.58</v>
+        <v>2.94</v>
       </c>
       <c r="O5" t="n">
-        <v>417243647350</v>
+        <v>119405625385</v>
       </c>
       <c r="P5" t="n">
-        <v>196800</v>
+        <v>16200</v>
       </c>
       <c r="Q5" t="n">
-        <v>27750</v>
+        <v>1206</v>
       </c>
       <c r="R5" t="n">
-        <v>52000</v>
+        <v>141000</v>
       </c>
       <c r="S5" t="n">
-        <v>96000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>애플 관련주로 부각되며 급등세 연출. 손바뀜 및 단기적 시세 분출 가능성 제기.</t>
+          <t>광통신 및 위성네트워크 섹터 내 우리로의 대장주 역할 부각. 양자주로서의 재료 풍부 및 13,000원 이상의 목표가 제시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['애플', '손바뀜', '단기 급등']</t>
+          <t>['광통신', '양자주', '대장주']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7740</v>
+        <v>8300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+15.52%</t>
+          <t>+11.86%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.79</v>
+        <v>0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>156</v>
       </c>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="G6" t="n">
-        <v>209</v>
+        <v>686</v>
       </c>
       <c r="H6" t="n">
-        <v>2.15</v>
+        <v>1.29</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,91 +963,91 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6700</v>
+        <v>7420</v>
       </c>
       <c r="K6" t="n">
-        <v>6530</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8370</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>6430</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.94</v>
+        <v>1.17</v>
       </c>
       <c r="O6" t="n">
-        <v>114032236005</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1206</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>광통신 및 위성네트워크 섹터 내 우리로의 대장주 역할 부각. 양자주로서의 재료 풍부 및 13,000원 이상의 목표가 제시.</t>
+          <t>페니트리움바이오의 임상 시험 디자인 및 데이터 발표에 대한 기대감. 기술 수출 및 텐버거 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '양자주', '대장주']</t>
+          <t>['임상 시험', '기술 수출', '텐버거']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8300</v>
+        <v>9930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+11.86%</t>
+          <t>+7.00%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>150</v>
+        <v>64</v>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>659</v>
+        <v>266</v>
       </c>
       <c r="H7" t="n">
-        <v>1.29</v>
+        <v>4.49</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7420</v>
+        <v>9280</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>10030</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>10880</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="N7" t="n">
-        <v>1.17</v>
+        <v>4.42</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>20108097150</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>15640</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5470</v>
       </c>
       <c r="R7" t="n">
-        <v>-12000</v>
+        <v>-88000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>핵심 기술 발표 임박 및 임상 시험 관련 기대감 형성. 일부 투자자들의 긍정적 전망.</t>
+          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['임상', '발표', '기술수출']</t>
+          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9980</v>
+        <v>15390</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+7.54%</t>
+          <t>+6.06%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.11</v>
       </c>
       <c r="E8" t="n">
-        <v>62</v>
+        <v>323</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="G8" t="n">
-        <v>250</v>
+        <v>809</v>
       </c>
       <c r="H8" t="n">
-        <v>4.49</v>
+        <v>3.14</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,143 +1147,143 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9280</v>
+        <v>14510</v>
       </c>
       <c r="K8" t="n">
-        <v>10030</v>
+        <v>17010</v>
       </c>
       <c r="L8" t="n">
-        <v>10880</v>
+        <v>17310</v>
       </c>
       <c r="M8" t="n">
-        <v>9800</v>
+        <v>15290</v>
       </c>
       <c r="N8" t="n">
-        <v>4.42</v>
+        <v>0.03</v>
       </c>
       <c r="O8" t="n">
-        <v>20037089230</v>
+        <v>172245668475</v>
       </c>
       <c r="P8" t="n">
-        <v>15640</v>
+        <v>36200</v>
       </c>
       <c r="Q8" t="n">
-        <v>5470</v>
+        <v>8920</v>
       </c>
       <c r="R8" t="n">
-        <v>-88000</v>
+        <v>-359000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
+          <t>중동 전쟁 우려 및 유가 급등에 따른 흥구석유의 3연상 기대감. 국제유가 변동성 관련 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
+          <t>['국제유가', '중동 전쟁', '전쟁 테마주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27400</v>
+        <v>1930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+4.98%</t>
+          <t>+1.53%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>0.32</v>
       </c>
       <c r="E9" t="n">
-        <v>217</v>
+        <v>103</v>
       </c>
       <c r="F9" t="n">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="G9" t="n">
-        <v>352</v>
+        <v>173</v>
       </c>
       <c r="H9" t="n">
-        <v>0.32</v>
+        <v>2.44</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>26100</v>
+        <v>1901</v>
       </c>
       <c r="K9" t="n">
-        <v>26350</v>
+        <v>2050</v>
       </c>
       <c r="L9" t="n">
-        <v>30300</v>
+        <v>2080</v>
       </c>
       <c r="M9" t="n">
-        <v>25400</v>
+        <v>1909</v>
       </c>
       <c r="N9" t="n">
-        <v>0.33</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>289258559675</v>
+        <v>37985063857</v>
       </c>
       <c r="P9" t="n">
-        <v>39350</v>
+        <v>4795</v>
       </c>
       <c r="Q9" t="n">
-        <v>8200</v>
+        <v>1524</v>
       </c>
       <c r="R9" t="n">
-        <v>7000</v>
+        <v>-591000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>하락장 속에서 외인 매수세 유입 관찰. 신규주로서 단기 급등 기대감 형성.</t>
+          <t>홍해 사태와 유가 상승에 따른 전쟁 테마주로서의 흥아해운 및 장금상선 관련 기대감. 외국인 매수 전환 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인 매수', '신규주', '단기 급등']</t>
+          <t>['홍해 사태', '유가 상승', '전쟁 테마주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1929</v>
+        <v>19620</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>+0.87%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.32</v>
+        <v>0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G10" t="n">
-        <v>170</v>
+        <v>399</v>
       </c>
       <c r="H10" t="n">
-        <v>2.44</v>
+        <v>10.65</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1901</v>
+        <v>19450</v>
       </c>
       <c r="K10" t="n">
-        <v>2050</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2080</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1909</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.12</v>
+        <v>10.64</v>
       </c>
       <c r="O10" t="n">
-        <v>37463516792</v>
+        <v>76504000000</v>
       </c>
       <c r="P10" t="n">
-        <v>4795</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1524</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-233000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-16000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>유가 상승 및 전쟁 테마주로 부각되며 단기적 상승 기대감 형성. 다만, 차익 실현 매물 출회 및 프로그램 매도세 관찰.</t>
+          <t>대차 해지 및 공매도 관련 논의 활발. 목표가 상향 뉴스 및 대규모 수주 기대감 형성.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['유가', '전쟁 테마주', '프로그램 매매']</t>
+          <t>['대차 해지', '공매도', '목표가 상향']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253000</v>
+        <v>90600</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.96</v>
+        <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="F11" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="G11" t="n">
-        <v>677</v>
+        <v>744</v>
       </c>
       <c r="H11" t="n">
-        <v>7.58</v>
+        <v>23.59</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>250500</v>
+        <v>89900</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>88700</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>91000</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="N11" t="n">
-        <v>8.539999999999999</v>
+        <v>23.65</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>111265779700</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>-298000</v>
+        <v>-264000</v>
       </c>
       <c r="S11" t="n">
-        <v>-18000</v>
+        <v>26000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>기관의 꾸준한 매수에도 불구하고 주가 하락. 공매도에 대한 불만 및 주가 방어 요구.</t>
+          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈에 따른 두산에너빌리티의 수혜 기대. 수주 잔고 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공매도', '기관매수', '주가방어']</t>
+          <t>['원전', '에너지 공급망', '수주 잔고']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50900</v>
+        <v>50700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+0.60%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.09</v>
       </c>
       <c r="E12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F12" t="n">
         <v>80</v>
       </c>
       <c r="G12" t="n">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H12" t="n">
         <v>38.78</v>
@@ -1530,7 +1530,7 @@
         <v>38.69</v>
       </c>
       <c r="O12" t="n">
-        <v>49723915825</v>
+        <v>51094893175</v>
       </c>
       <c r="P12" t="n">
         <v>67300</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>53600</v>
+        <v>53400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.75%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.44</v>
       </c>
       <c r="E13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F13" t="n">
         <v>37</v>
       </c>
       <c r="G13" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H13" t="n">
         <v>2.92</v>
@@ -1622,7 +1622,7 @@
         <v>3.36</v>
       </c>
       <c r="O13" t="n">
-        <v>79770000000</v>
+        <v>81210000000</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>415000</v>
+        <v>416000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H14" t="n">
         <v>38.02</v>
@@ -1714,7 +1714,7 @@
         <v>37.82</v>
       </c>
       <c r="O14" t="n">
-        <v>40522524500</v>
+        <v>41726120500</v>
       </c>
       <c r="P14" t="n">
         <v>822000</v>
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19710</v>
+        <v>1853000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="E15" t="n">
-        <v>122</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>76</v>
+        <v>458</v>
       </c>
       <c r="G15" t="n">
-        <v>395</v>
+        <v>1179</v>
       </c>
       <c r="H15" t="n">
-        <v>10.65</v>
+        <v>50.55</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>19750</v>
+        <v>1856000</v>
       </c>
       <c r="K15" t="n">
-        <v>19500</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>19840</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>19060</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>10.64</v>
+        <v>50.67</v>
       </c>
       <c r="O15" t="n">
-        <v>74714791305</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-249000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-102000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대차 해지 및 공매도 관련 논의 활발. 목표가 상향 뉴스 및 대규모 수주 기대감 형성.</t>
+          <t>AI 클라우드 수요 증가 관련 뉴스 일부 확인. 시장 전반의 하락세 속에서 일부 반등 기대감 존재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['대차 해지', '공매도', '목표가 상향']</t>
+          <t>['AI', '실적', '하락세']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,130 +1844,130 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14480</v>
+        <v>14830</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.82%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F16" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="G16" t="n">
-        <v>431</v>
+        <v>218</v>
       </c>
       <c r="H16" t="n">
-        <v>5.98</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14600</v>
+        <v>15040</v>
       </c>
       <c r="K16" t="n">
-        <v>14800</v>
+        <v>14550</v>
       </c>
       <c r="L16" t="n">
-        <v>14950</v>
+        <v>15260</v>
       </c>
       <c r="M16" t="n">
-        <v>14020</v>
+        <v>14350</v>
       </c>
       <c r="N16" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>80126434970</v>
+        <v>16451373315</v>
       </c>
       <c r="P16" t="n">
-        <v>30200</v>
+        <v>19380</v>
       </c>
       <c r="Q16" t="n">
-        <v>3540</v>
+        <v>3200</v>
       </c>
       <c r="R16" t="n">
-        <v>-371000</v>
+        <v>22000</v>
       </c>
       <c r="S16" t="n">
-        <v>-69000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>원전 관련주로 언급되며 상승 기대감 형성. 특정 세력의 개입 및 단기 과열 가능성 제기.</t>
+          <t>금호건설, 호남 반도체 부지 100만평 추가 확보 검토 및 삼성전자 신축 공장 수주 소식. 친환경 및 폐기물 처리 사업 관련 성장성 기대.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', '단기 과열', '외인 매매']</t>
+          <t>['반도체 부지', '신축 공장 수주', '친환경']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29550</v>
+        <v>8820</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="F17" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
-        <v>121</v>
+        <v>206</v>
       </c>
       <c r="H17" t="n">
-        <v>25.55</v>
+        <v>27.19</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>29800</v>
+        <v>8950</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>24.99</v>
+        <v>27.16</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>13437000000</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1999,14 +1999,14 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>265000</v>
+        <v>-100000</v>
       </c>
       <c r="S17" t="n">
-        <v>-69000</v>
+        <v>-78000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>주가 상승에 대한 강한 불만과 함께 회사의 실적 부진 및 저평가에 대한 부정적인 인식이 지배적임.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['저평가', '실적 부진', '금리 인상']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3570</v>
+        <v>14380</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>99</v>
+        <v>444</v>
       </c>
       <c r="H18" t="n">
-        <v>0.73</v>
+        <v>5.98</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,130 +2067,130 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>3620</v>
+        <v>14600</v>
       </c>
       <c r="K18" t="n">
-        <v>3725</v>
+        <v>14800</v>
       </c>
       <c r="L18" t="n">
-        <v>3915</v>
+        <v>14950</v>
       </c>
       <c r="M18" t="n">
-        <v>3550</v>
+        <v>14020</v>
       </c>
       <c r="N18" t="n">
-        <v>1.54</v>
+        <v>6.09</v>
       </c>
       <c r="O18" t="n">
-        <v>37804221054</v>
+        <v>82776313510</v>
       </c>
       <c r="P18" t="n">
-        <v>4335</v>
+        <v>30200</v>
       </c>
       <c r="Q18" t="n">
-        <v>1246</v>
+        <v>3540</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-371000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-69000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>원자력 발전 관련주로서의 우리기술에 대한 기대감과 함께 단기 과열 및 변동성에 대한 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['원전', '단기 과열', '변동성']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8810</v>
+        <v>12340</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-2.30%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.03</v>
+        <v>0.8</v>
       </c>
       <c r="E19" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>205</v>
+        <v>60</v>
       </c>
       <c r="H19" t="n">
-        <v>27.19</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8970</v>
+        <v>12630</v>
       </c>
       <c r="K19" t="n">
-        <v>8780</v>
+        <v>12520</v>
       </c>
       <c r="L19" t="n">
-        <v>8880</v>
+        <v>12930</v>
       </c>
       <c r="M19" t="n">
-        <v>8680</v>
+        <v>12010</v>
       </c>
       <c r="N19" t="n">
-        <v>27.16</v>
+        <v>0.14</v>
       </c>
       <c r="O19" t="n">
-        <v>12941152720</v>
+        <v>37278083370</v>
       </c>
       <c r="P19" t="n">
-        <v>17950</v>
+        <v>20850</v>
       </c>
       <c r="Q19" t="n">
-        <v>8120</v>
+        <v>4020</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>-69000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 강한 불만과 함께 회사의 실적 부진 및 저평가에 대한 부정적인 인식이 지배적임.</t>
+          <t>원전 테마주로서의 삼미금속 언급. 한전기술 등 타 원전주들의 급등 속 상대적 부진 및 거래량 부족에 대한 지적.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['저평가', '실적 부진', '금리 인상']</t>
+          <t>['원전', '테마주', '거래량']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>89900</v>
+        <v>28650</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-3.05%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.06</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>177</v>
+        <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="G20" t="n">
-        <v>733</v>
+        <v>131</v>
       </c>
       <c r="H20" t="n">
-        <v>23.59</v>
+        <v>51.3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,152 +2251,152 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>91700</v>
+        <v>29550</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>28650</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>28900</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>28500</v>
       </c>
       <c r="N20" t="n">
-        <v>23.65</v>
+        <v>24.99</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>34598107725</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>31200</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="R20" t="n">
-        <v>-264000</v>
+        <v>265000</v>
       </c>
       <c r="S20" t="n">
-        <v>26000</v>
+        <v>-69000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 투자 협상 마무리 및 원전 수주 기대감. 29.7조원 수주잔고 기반 상승 전망.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전', '수주', '미국 투자']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>192500</v>
+        <v>14270</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.53%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.39</v>
       </c>
       <c r="E21" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F21" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G21" t="n">
-        <v>121</v>
+        <v>206</v>
       </c>
       <c r="H21" t="n">
-        <v>75.98999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>197500</v>
+        <v>14740</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>14050</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>14560</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>14030</v>
       </c>
       <c r="N21" t="n">
-        <v>75.92</v>
+        <v>2.89</v>
       </c>
       <c r="O21" t="n">
-        <v>354454000000</v>
+        <v>44413578525</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R21" t="n">
-        <v>-852000</v>
+        <v>-128000</v>
       </c>
       <c r="S21" t="n">
-        <v>-123000</v>
+        <v>-6000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 증시 하락 및 기관/외인 매도세로 주가 하락 압력을 받으며, 배당금 대비 주가 하락에 대한 불만이 나타남.</t>
+          <t>국내외 통신 관련 사업 확장에 따른 대한광통신의 상승 기대감. 외국인 및 기관 매수세 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['우선주', '기관 매도', '미국 증시']</t>
+          <t>['광통신', '외국인 매수', '기관 매수']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7420</v>
+        <v>7410</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.39%</t>
+          <t>-3.52%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F22" t="n">
         <v>54</v>
       </c>
       <c r="G22" t="n">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="H22" t="n">
         <v>11.72</v>
@@ -2450,7 +2450,7 @@
         <v>11.62</v>
       </c>
       <c r="O22" t="n">
-        <v>7854366540</v>
+        <v>8021693995</v>
       </c>
       <c r="P22" t="n">
         <v>8850</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>주가 관련 다양한 추측성 언급 및 단기 매매 전략 논의. 뚜렷한 근거 기반 정보 부족.</t>
+          <t>주가 상승을 저해하는 요인들과 함께 기관 및 외인 수급 관련 불확실성 언급. 단기적인 주가 변동성 예측.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['주가', '매매', '전략']</t>
+          <t>['기관 수급', '외인 수급', '주가 변동성']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2495,31 +2495,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1785000</v>
+        <v>258000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.67%</t>
+          <t>-4.27%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="E23" t="n">
         <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>463</v>
+        <v>513</v>
       </c>
       <c r="G23" t="n">
-        <v>1181</v>
+        <v>1605</v>
       </c>
       <c r="H23" t="n">
-        <v>50.55</v>
+        <v>46.71</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,51 +2527,51 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1853000</v>
+        <v>269500</v>
       </c>
       <c r="K23" t="n">
-        <v>1773000</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1795000</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1768000</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>50.67</v>
+        <v>46.81</v>
       </c>
       <c r="O23" t="n">
-        <v>2284635417000</v>
+        <v>1781968000000</v>
       </c>
       <c r="P23" t="n">
-        <v>2987000</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>305500</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>-249000</v>
+        <v>-1232000</v>
       </c>
       <c r="S23" t="n">
-        <v>-102000</v>
+        <v>-646000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>AI 클라우드 수요 증가 관련 뉴스 일부 확인. 시장 전반의 하락세 속에서 일부 반등 기대감 존재.</t>
+          <t>반도체 수출 역대 최대 기록에도 불구하고 주가 하락에 대한 불만 토로. 시장 상황 및 정치적 요인 언급.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['AI', '실적', '하락세']</t>
+          <t>['반도체 수출', '주가 하락', '시장 상황']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,38 +2580,38 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15040</v>
+        <v>192600</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-3.84%</t>
+          <t>-5.12%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="F24" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G24" t="n">
-        <v>217</v>
+        <v>124</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,38 +2619,38 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>15640</v>
+        <v>203000</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>195000</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>195600</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>191000</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>75.92</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>359787180200</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>243500</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>58600</v>
       </c>
       <c r="R24" t="n">
-        <v>22000</v>
+        <v>-852000</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>-123000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>금호건설, 호남 반도체 부지 100만평 추가 확보 검토 및 삼성전자 신축 공장 수주 소식. 친환경 및 폐기물 처리 사업 관련 성장성 기대.</t>
+          <t>미국 증시 하락 및 기관/외인 매도세로 주가 하락 압력을 받으며, 배당금 대비 주가 하락에 대한 불만이 나타남.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['반도체 부지', '신축 공장 수주', '친환경']</t>
+          <t>['우선주', '기관 매도', '미국 증시']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,169 +2672,169 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>257750</v>
+        <v>3560</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-4.18%</t>
+          <t>-7.89%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.1</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>800</v>
+        <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>508</v>
+        <v>31</v>
       </c>
       <c r="G25" t="n">
-        <v>1640</v>
+        <v>96</v>
       </c>
       <c r="H25" t="n">
-        <v>46.71</v>
+        <v>0.73</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>269000</v>
+        <v>3865</v>
       </c>
       <c r="K25" t="n">
-        <v>258000</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>261000</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>257500</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>46.81</v>
+        <v>1.54</v>
       </c>
       <c r="O25" t="n">
-        <v>1694276205500</v>
+        <v>38116000000</v>
       </c>
       <c r="P25" t="n">
-        <v>374500</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>72100</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>-1232000</v>
+        <v>64000</v>
       </c>
       <c r="S25" t="n">
-        <v>-646000</v>
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>반도체 수출 역대 최대 기록에도 불구하고 주가 하락. 개인 투자자들의 완전 승리 및 외인 매수세 관찰.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['반도체 수출', '영업이익', '외인 매수']</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14330</v>
+        <v>233000</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-4.21%</t>
+          <t>-7.91%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.39</v>
+        <v>-0.96</v>
       </c>
       <c r="E26" t="n">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="F26" t="n">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="G26" t="n">
-        <v>202</v>
+        <v>678</v>
       </c>
       <c r="H26" t="n">
-        <v>2.5</v>
+        <v>7.58</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>14960</v>
+        <v>253000</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>231000</v>
       </c>
       <c r="N26" t="n">
-        <v>2.89</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>42540000000</v>
+        <v>163918301750</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>426000</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>86100</v>
       </c>
       <c r="R26" t="n">
-        <v>-128000</v>
+        <v>-298000</v>
       </c>
       <c r="S26" t="n">
-        <v>-6000</v>
+        <v>-18000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>광통신 섹터의 상승 기대감 속에서 외국인 매수세 유입. 2만원 목표가 제시 및 장기 보유 관점.</t>
+          <t>기관의 꾸준한 매수에도 불구하고 주가 하락. 공매도에 대한 불만 및 주가 방어 요구.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -2843,11 +2843,11 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['광통신', '외국인 매수', '장기 보유']</t>
+          <t>['공매도', '기관매수', '주가방어']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,38 +2856,38 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12310</v>
+        <v>27350</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-5.53%</t>
+          <t>-9.74%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.8</v>
+        <v>-0.01</v>
       </c>
       <c r="E27" t="n">
-        <v>58</v>
+        <v>219</v>
       </c>
       <c r="F27" t="n">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>351</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>13030</v>
+        <v>30300</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="O27" t="n">
-        <v>35632000000</v>
+        <v>291382000000</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2919,36 +2919,36 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>-69000</v>
+        <v>7000</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>원전 테마주로서의 삼미금속 언급. 한전기술 등 타 원전주들의 급등 속 상대적 부진 및 거래량 부족에 대한 지적.</t>
+          <t>신규 상장주로서의 스카이랩스에 대한 기대감. 외인 수급 및 단기 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['원전', '테마주', '거래량']</t>
+          <t>['신규주', '외인 수급', '단기 급등']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>386380</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260911_11.xlsx
+++ b/data/trending_integrated_20260911_11.xlsx
@@ -584,7 +584,7 @@
         <v>88</v>
       </c>
       <c r="G2" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H2" t="n">
         <v>2.39</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>206661000000</v>
+        <v>206811000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>젠슨 황의 AI 다음 핵심 시장으로 사이버 보안 부문 지목에 따른 엑스게이트의 급등 기대. 양자보안 관련 내용 포함.</t>
+          <t>젠슨 황의 AI 다음 시장으로 사이버 보안 지목, 양자 보안 기술 부각 및 상한가 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['사이버 보안', '젠슨 황', '양자보안']</t>
+          <t>['젠슨 황', '사이버 보안', '양자 보안']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,79 +655,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>138300</v>
+        <v>2535</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+19.53%</t>
+          <t>+19.29%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.26</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="G3" t="n">
-        <v>194</v>
+        <v>80</v>
       </c>
       <c r="H3" t="n">
-        <v>4.32</v>
+        <v>3.83</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>115700</v>
+        <v>2125</v>
       </c>
       <c r="K3" t="n">
-        <v>112100</v>
+        <v>2230</v>
       </c>
       <c r="L3" t="n">
-        <v>147500</v>
+        <v>2692</v>
       </c>
       <c r="M3" t="n">
-        <v>112000</v>
+        <v>2170</v>
       </c>
       <c r="N3" t="n">
-        <v>4.58</v>
+        <v>3.76</v>
       </c>
       <c r="O3" t="n">
-        <v>421628622150</v>
+        <v>87117913382</v>
       </c>
       <c r="P3" t="n">
-        <v>196800</v>
+        <v>4810</v>
       </c>
       <c r="Q3" t="n">
-        <v>27750</v>
+        <v>1400</v>
       </c>
       <c r="R3" t="n">
-        <v>52000</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>96000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>애플 관련주로 부각되며 급등세 연출. 손바뀜 및 단기적 시세 분출 가능성 제기.</t>
+          <t>젠슨 황의 사이버보안 섹터 지목과 함께 양자컴퓨터 보조금 지원 소식 언급. 드림시큐리티의 대장주로서의 부각 및 상승 신호.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['애플', '손바뀜', '단기 급등']</t>
+          <t>['젠슨황', '사이버보안', '양자컴퓨터']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,91 +735,91 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2530</v>
+        <v>137800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+19.06%</t>
+          <t>+19.10%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.26</v>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G4" t="n">
-        <v>72</v>
+        <v>206</v>
       </c>
       <c r="H4" t="n">
-        <v>3.83</v>
+        <v>4.32</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2125</v>
+        <v>115700</v>
       </c>
       <c r="K4" t="n">
-        <v>2230</v>
+        <v>112100</v>
       </c>
       <c r="L4" t="n">
-        <v>2692</v>
+        <v>147500</v>
       </c>
       <c r="M4" t="n">
-        <v>2170</v>
+        <v>112000</v>
       </c>
       <c r="N4" t="n">
-        <v>3.76</v>
+        <v>4.58</v>
       </c>
       <c r="O4" t="n">
-        <v>86322008419</v>
+        <v>424273741850</v>
       </c>
       <c r="P4" t="n">
-        <v>4810</v>
+        <v>196800</v>
       </c>
       <c r="Q4" t="n">
-        <v>1400</v>
+        <v>27750</v>
       </c>
       <c r="R4" t="n">
-        <v>-1884000</v>
+        <v>52000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>96000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>젠슨 황의 사이버보안 섹터 지목과 함께 양자컴퓨터 보조금 지원 소식 언급. 드림시큐리티의 대장주로서의 부각 및 상승 신호.</t>
+          <t>애플 관련 일회성 호재로 인한 단기 급등 후 손바뀜 현상 발생.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['젠슨황', '사이버보안', '양자컴퓨터']</t>
+          <t>['애플', '일회성 호재', '손바뀜']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,12 +827,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>001820</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7590</v>
+        <v>7760</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+13.28%</t>
+          <t>+18.11%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.79</v>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H5" t="n">
         <v>2.15</v>
@@ -871,28 +871,28 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6700</v>
+        <v>6570</v>
       </c>
       <c r="K5" t="n">
-        <v>6530</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>8370</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>6430</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>2.94</v>
       </c>
       <c r="O5" t="n">
-        <v>119405625385</v>
+        <v>124471000000</v>
       </c>
       <c r="P5" t="n">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1206</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>141000</v>
@@ -946,13 +946,13 @@
         <v>0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F6" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G6" t="n">
-        <v>686</v>
+        <v>708</v>
       </c>
       <c r="H6" t="n">
         <v>1.29</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>페니트리움바이오의 임상 시험 디자인 및 데이터 발표에 대한 기대감. 기술 수출 및 텐버거 가능성 언급.</t>
+          <t>WCLC 학회 발표 기반 기술 수출 가능성, 세계 최초 폐암학회 발표 임박.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['임상 시험', '기술 수출', '텐버거']</t>
+          <t>['WCLC', '기술 수출', '폐암학회']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,79 +1023,79 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9930</v>
+        <v>7680</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+7.00%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E7" t="n">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G7" t="n">
-        <v>266</v>
+        <v>326</v>
       </c>
       <c r="H7" t="n">
-        <v>4.49</v>
+        <v>11.72</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9280</v>
+        <v>7100</v>
       </c>
       <c r="K7" t="n">
-        <v>10030</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>10880</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>9800</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.42</v>
+        <v>11.62</v>
       </c>
       <c r="O7" t="n">
-        <v>20108097150</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>15640</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5470</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-88000</v>
+        <v>43000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
+          <t>기사 기반 호재 및 기관 매수세 유입 가능성 언급, 전고점 돌파 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
+          <t>['호재', '기관 매수', '전고점']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15390</v>
+        <v>15520</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+6.06%</t>
+          <t>+6.96%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>3.11</v>
       </c>
       <c r="E8" t="n">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="F8" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G8" t="n">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="H8" t="n">
         <v>3.14</v>
@@ -1162,7 +1162,7 @@
         <v>0.03</v>
       </c>
       <c r="O8" t="n">
-        <v>172245668475</v>
+        <v>175203851810</v>
       </c>
       <c r="P8" t="n">
         <v>36200</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1930</v>
+        <v>1923</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>103</v>
       </c>
       <c r="F9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G9" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H9" t="n">
         <v>2.44</v>
@@ -1254,7 +1254,7 @@
         <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>37985063857</v>
+        <v>38277324076</v>
       </c>
       <c r="P9" t="n">
         <v>4795</v>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19620</v>
+        <v>253000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.01</v>
+        <v>-0.96</v>
       </c>
       <c r="E10" t="n">
-        <v>126</v>
+        <v>202</v>
       </c>
       <c r="F10" t="n">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="G10" t="n">
-        <v>399</v>
+        <v>693</v>
       </c>
       <c r="H10" t="n">
-        <v>10.65</v>
+        <v>7.58</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>19450</v>
+        <v>250500</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>10.64</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>76504000000</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1355,14 +1355,14 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-233000</v>
+        <v>-298000</v>
       </c>
       <c r="S10" t="n">
-        <v>-16000</v>
+        <v>-18000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대차 해지 및 공매도 관련 논의 활발. 목표가 상향 뉴스 및 대규모 수주 기대감 형성.</t>
+          <t>기관의 꾸준한 매수에도 불구하고 주가 하락. 공매도에 대한 불만 및 주가 방어 요구.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['대차 해지', '공매도', '목표가 상향']</t>
+          <t>['공매도', '기관매수', '주가방어']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>90600</v>
+        <v>50900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="F11" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="G11" t="n">
-        <v>744</v>
+        <v>504</v>
       </c>
       <c r="H11" t="n">
-        <v>23.59</v>
+        <v>38.78</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>89900</v>
+        <v>50400</v>
       </c>
       <c r="K11" t="n">
-        <v>88700</v>
+        <v>50500</v>
       </c>
       <c r="L11" t="n">
-        <v>91000</v>
+        <v>51200</v>
       </c>
       <c r="M11" t="n">
-        <v>88000</v>
+        <v>49650</v>
       </c>
       <c r="N11" t="n">
-        <v>23.65</v>
+        <v>38.69</v>
       </c>
       <c r="O11" t="n">
-        <v>111265779700</v>
+        <v>52252753025</v>
       </c>
       <c r="P11" t="n">
-        <v>139200</v>
+        <v>67300</v>
       </c>
       <c r="Q11" t="n">
-        <v>57000</v>
+        <v>23150</v>
       </c>
       <c r="R11" t="n">
-        <v>-264000</v>
+        <v>-134000</v>
       </c>
       <c r="S11" t="n">
-        <v>26000</v>
+        <v>2000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈에 따른 두산에너빌리티의 수혜 기대. 수주 잔고 언급.</t>
+          <t>약 4.7조원 규모의 대규모 수주 공시 확인. 사우디 및 베트남 관련 복합 호재 기대감 형성.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전', '에너지 공급망', '수주 잔고']</t>
+          <t>['수주', '공시', '호재']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50700</v>
+        <v>53300</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.60%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.09</v>
+        <v>-0.44</v>
       </c>
       <c r="E12" t="n">
-        <v>135</v>
+        <v>64</v>
       </c>
       <c r="F12" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>501</v>
+        <v>128</v>
       </c>
       <c r="H12" t="n">
-        <v>38.78</v>
+        <v>2.92</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,91 +1515,91 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>50400</v>
+        <v>53200</v>
       </c>
       <c r="K12" t="n">
-        <v>50500</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>51200</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>49650</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>38.69</v>
+        <v>3.36</v>
       </c>
       <c r="O12" t="n">
-        <v>51094893175</v>
+        <v>82646000000</v>
       </c>
       <c r="P12" t="n">
-        <v>67300</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>23150</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-134000</v>
+        <v>116000</v>
       </c>
       <c r="S12" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>약 4.7조원 규모의 대규모 수주 공시 확인. 사우디 및 베트남 관련 복합 호재 기대감 형성.</t>
+          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['수주', '공시', '호재']</t>
+          <t>['태양광', '고유가', '신호가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>475150</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>53400</v>
+        <v>416000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.44</v>
+        <v>0.2</v>
       </c>
       <c r="E13" t="n">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="F13" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="H13" t="n">
-        <v>2.92</v>
+        <v>38.02</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,47 +1607,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>53200</v>
+        <v>415500</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>407000</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>418000</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>404000</v>
       </c>
       <c r="N13" t="n">
-        <v>3.36</v>
+        <v>37.82</v>
       </c>
       <c r="O13" t="n">
-        <v>81210000000</v>
+        <v>42625118000</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>822000</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>283000</v>
       </c>
       <c r="R13" t="n">
-        <v>116000</v>
+        <v>13000</v>
       </c>
       <c r="S13" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>고유가 시대 속 태양광 섹터 언급 및 SK이터닉스의 상방 추세 전환 기대. 신고가 갱신 및 호재성 뉴스 기대.</t>
+          <t>로봇 사업 확장 및 신기술 공개로 인한 수주 기대감. 유럽 중국차 관세 관련 호재 및 저평가 논의.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['태양광', '고유가', '신호가']</t>
+          <t>['로봇 사업', '수주', '관세']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1655,43 +1655,43 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>012330</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>416000</v>
+        <v>19680</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="F14" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="G14" t="n">
-        <v>211</v>
+        <v>407</v>
       </c>
       <c r="H14" t="n">
-        <v>38.02</v>
+        <v>10.65</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>415500</v>
+        <v>19750</v>
       </c>
       <c r="K14" t="n">
-        <v>407000</v>
+        <v>19500</v>
       </c>
       <c r="L14" t="n">
-        <v>418000</v>
+        <v>19840</v>
       </c>
       <c r="M14" t="n">
-        <v>404000</v>
+        <v>19060</v>
       </c>
       <c r="N14" t="n">
-        <v>37.82</v>
+        <v>10.64</v>
       </c>
       <c r="O14" t="n">
-        <v>41726120500</v>
+        <v>77968768755</v>
       </c>
       <c r="P14" t="n">
-        <v>822000</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>283000</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>로봇 사업 확장 및 신기술 공개로 인한 수주 기대감. 유럽 중국차 관세 관련 호재 및 저평가 논의.</t>
+          <t>대차 해지 및 공매도 관련 논의 활발. 목표가 상향 뉴스 및 대규모 수주 기대감 형성.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['로봇 사업', '수주', '관세']</t>
+          <t>['대차 해지', '공매도', '목표가 상향']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1853000</v>
+        <v>29550</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.12</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>458</v>
+        <v>37</v>
       </c>
       <c r="G15" t="n">
-        <v>1179</v>
+        <v>131</v>
       </c>
       <c r="H15" t="n">
-        <v>50.55</v>
+        <v>25.55</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1856000</v>
+        <v>29800</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1803,7 +1803,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>50.67</v>
+        <v>24.99</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1815,67 +1815,67 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-249000</v>
+        <v>265000</v>
       </c>
       <c r="S15" t="n">
-        <v>-102000</v>
+        <v>-69000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI 클라우드 수요 증가 관련 뉴스 일부 확인. 시장 전반의 하락세 속에서 일부 반등 기대감 존재.</t>
+          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI', '실적', '하락세']</t>
+          <t>['유럽 자금', '환율', '유가']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14830</v>
+        <v>8840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="G16" t="n">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>27.19</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>15040</v>
+        <v>8970</v>
       </c>
       <c r="K16" t="n">
-        <v>14550</v>
+        <v>8780</v>
       </c>
       <c r="L16" t="n">
-        <v>15260</v>
+        <v>8880</v>
       </c>
       <c r="M16" t="n">
-        <v>14350</v>
+        <v>8680</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>27.16</v>
       </c>
       <c r="O16" t="n">
-        <v>16451373315</v>
+        <v>13774947895</v>
       </c>
       <c r="P16" t="n">
-        <v>19380</v>
+        <v>17950</v>
       </c>
       <c r="Q16" t="n">
-        <v>3200</v>
+        <v>8120</v>
       </c>
       <c r="R16" t="n">
-        <v>22000</v>
+        <v>-100000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-78000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>금호건설, 호남 반도체 부지 100만평 추가 확보 검토 및 삼성전자 신축 공장 수주 소식. 친환경 및 폐기물 처리 사업 관련 성장성 기대.</t>
+          <t>주가 상승에 대한 강한 불만과 함께 회사의 실적 부진 및 저평가에 대한 부정적인 인식이 지배적임.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['반도체 부지', '신축 공장 수주', '친환경']</t>
+          <t>['저평가', '실적 부진', '금리 인상']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,77 +1936,77 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8820</v>
+        <v>3565</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>-1.52%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.03</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="G17" t="n">
-        <v>206</v>
+        <v>97</v>
       </c>
       <c r="H17" t="n">
-        <v>27.19</v>
+        <v>0.73</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8950</v>
+        <v>3620</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>3725</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3915</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3550</v>
       </c>
       <c r="N17" t="n">
-        <v>27.16</v>
+        <v>1.54</v>
       </c>
       <c r="O17" t="n">
-        <v>13437000000</v>
+        <v>38540348105</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4335</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1246</v>
       </c>
       <c r="R17" t="n">
-        <v>-100000</v>
+        <v>64000</v>
       </c>
       <c r="S17" t="n">
-        <v>-78000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 강한 불만과 함께 회사의 실적 부진 및 저평가에 대한 부정적인 인식이 지배적임.</t>
+          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['저평가', '실적 부진', '금리 인상']</t>
+          <t>['폭락', '주주', '전망']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,90 +2028,90 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14380</v>
+        <v>89900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.11</v>
+        <v>-0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="G18" t="n">
-        <v>444</v>
+        <v>757</v>
       </c>
       <c r="H18" t="n">
-        <v>5.98</v>
+        <v>23.59</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>14600</v>
+        <v>91700</v>
       </c>
       <c r="K18" t="n">
-        <v>14800</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>14950</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>14020</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>6.09</v>
+        <v>23.65</v>
       </c>
       <c r="O18" t="n">
-        <v>82776313510</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>30200</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3540</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-371000</v>
+        <v>-264000</v>
       </c>
       <c r="S18" t="n">
-        <v>-69000</v>
+        <v>26000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>원자력 발전 관련주로서의 우리기술에 대한 기대감과 함께 단기 과열 및 변동성에 대한 언급.</t>
+          <t>미국 투자 협상 마무리 및 중동 에너지 공급망 이슈에 따른 두산에너빌리티의 수혜 기대. 수주 잔고 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전', '단기 과열', '변동성']</t>
+          <t>['원전', '에너지 공급망', '수주 잔고']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12340</v>
+        <v>193000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.30%</t>
+          <t>-2.28%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.8</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F19" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>126</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9399999999999999</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>12630</v>
+        <v>197500</v>
       </c>
       <c r="K19" t="n">
-        <v>12520</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>12930</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>12010</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.14</v>
+        <v>75.92</v>
       </c>
       <c r="O19" t="n">
-        <v>37278083370</v>
+        <v>365658000000</v>
       </c>
       <c r="P19" t="n">
-        <v>20850</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4020</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>-69000</v>
+        <v>-852000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-123000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>원전 테마주로서의 삼미금속 언급. 한전기술 등 타 원전주들의 급등 속 상대적 부진 및 거래량 부족에 대한 지적.</t>
+          <t>미국 증시 하락 및 기관/외인 매도세로 주가 하락 압력을 받으며, 배당금 대비 주가 하락에 대한 불만이 나타남.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', '테마주', '거래량']</t>
+          <t>['우선주', '기관 매도', '미국 증시']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,130 +2212,130 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>28650</v>
+        <v>14260</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.05%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="E20" t="n">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="F20" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G20" t="n">
-        <v>131</v>
+        <v>462</v>
       </c>
       <c r="H20" t="n">
-        <v>51.3</v>
+        <v>5.98</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>29550</v>
+        <v>14600</v>
       </c>
       <c r="K20" t="n">
-        <v>28650</v>
+        <v>14800</v>
       </c>
       <c r="L20" t="n">
-        <v>28900</v>
+        <v>14950</v>
       </c>
       <c r="M20" t="n">
-        <v>28500</v>
+        <v>14020</v>
       </c>
       <c r="N20" t="n">
-        <v>24.99</v>
+        <v>6.09</v>
       </c>
       <c r="O20" t="n">
-        <v>34598107725</v>
+        <v>84584505165</v>
       </c>
       <c r="P20" t="n">
-        <v>31200</v>
+        <v>30200</v>
       </c>
       <c r="Q20" t="n">
-        <v>21000</v>
+        <v>3540</v>
       </c>
       <c r="R20" t="n">
-        <v>265000</v>
+        <v>-371000</v>
       </c>
       <c r="S20" t="n">
         <v>-69000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>유럽 자금의 매수세 유입 기대감 속에서 단기 조정 가능성과 함께 환율 및 유가 변동성에 영향을 받고 있음.</t>
+          <t>원전 관련주 부각, 모건 증권 매수세 유입 및 상한가 기대.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['유럽 자금', '환율', '유가']</t>
+          <t>['원전', '모건 증권', '상한가']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14270</v>
+        <v>12290</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.19%</t>
+          <t>-2.69%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.39</v>
+        <v>0.8</v>
       </c>
       <c r="E21" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F21" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G21" t="n">
-        <v>206</v>
+        <v>61</v>
       </c>
       <c r="H21" t="n">
-        <v>2.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,143 +2343,143 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>14740</v>
+        <v>12630</v>
       </c>
       <c r="K21" t="n">
-        <v>14050</v>
+        <v>12520</v>
       </c>
       <c r="L21" t="n">
-        <v>14560</v>
+        <v>12930</v>
       </c>
       <c r="M21" t="n">
-        <v>14030</v>
+        <v>12010</v>
       </c>
       <c r="N21" t="n">
-        <v>2.89</v>
+        <v>0.14</v>
       </c>
       <c r="O21" t="n">
-        <v>44413578525</v>
+        <v>37654592555</v>
       </c>
       <c r="P21" t="n">
-        <v>31500</v>
+        <v>20850</v>
       </c>
       <c r="Q21" t="n">
-        <v>1272</v>
+        <v>4020</v>
       </c>
       <c r="R21" t="n">
-        <v>-128000</v>
+        <v>-69000</v>
       </c>
       <c r="S21" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>국내외 통신 관련 사업 확장에 따른 대한광통신의 상승 기대감. 외국인 및 기관 매수세 언급.</t>
+          <t>원전 테마주로서의 삼미금속 언급. 한전기술 등 타 원전주들의 급등 속 상대적 부진 및 거래량 부족에 대한 지적.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['광통신', '외국인 매수', '기관 매수']</t>
+          <t>['원전', '테마주', '거래량']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7410</v>
+        <v>14260</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>-3.26%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.1</v>
+        <v>-0.39</v>
       </c>
       <c r="E22" t="n">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="F22" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G22" t="n">
-        <v>323</v>
+        <v>211</v>
       </c>
       <c r="H22" t="n">
-        <v>11.72</v>
+        <v>2.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>7680</v>
+        <v>14740</v>
       </c>
       <c r="K22" t="n">
-        <v>7540</v>
+        <v>14050</v>
       </c>
       <c r="L22" t="n">
-        <v>7660</v>
+        <v>14560</v>
       </c>
       <c r="M22" t="n">
-        <v>7390</v>
+        <v>14030</v>
       </c>
       <c r="N22" t="n">
-        <v>11.62</v>
+        <v>2.89</v>
       </c>
       <c r="O22" t="n">
-        <v>8021693995</v>
+        <v>45632558890</v>
       </c>
       <c r="P22" t="n">
-        <v>8850</v>
+        <v>31500</v>
       </c>
       <c r="Q22" t="n">
-        <v>4220</v>
+        <v>1272</v>
       </c>
       <c r="R22" t="n">
-        <v>43000</v>
+        <v>-128000</v>
       </c>
       <c r="S22" t="n">
-        <v>-2000</v>
+        <v>-6000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>주가 상승을 저해하는 요인들과 함께 기관 및 외인 수급 관련 불확실성 언급. 단기적인 주가 변동성 예측.</t>
+          <t>국내외 통신 관련 사업 확장에 따른 대한광통신의 상승 기대감. 외국인 및 기관 매수세 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['기관 수급', '외인 수급', '주가 변동성']</t>
+          <t>['광통신', '외국인 매수', '기관 매수']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>258000</v>
+        <v>1789000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-4.27%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="E23" t="n">
         <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>513</v>
+        <v>463</v>
       </c>
       <c r="G23" t="n">
-        <v>1605</v>
+        <v>1192</v>
       </c>
       <c r="H23" t="n">
-        <v>46.71</v>
+        <v>50.55</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,51 +2527,51 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>269500</v>
+        <v>1853000</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1773000</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1795000</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1768000</v>
       </c>
       <c r="N23" t="n">
-        <v>46.81</v>
+        <v>50.67</v>
       </c>
       <c r="O23" t="n">
-        <v>1781968000000</v>
+        <v>2406876100000</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2987000</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>305500</v>
       </c>
       <c r="R23" t="n">
-        <v>-1232000</v>
+        <v>-249000</v>
       </c>
       <c r="S23" t="n">
-        <v>-646000</v>
+        <v>-102000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>반도체 수출 역대 최대 기록에도 불구하고 주가 하락에 대한 불만 토로. 시장 상황 및 정치적 요인 언급.</t>
+          <t>외국인 및 기관 매도세 속 주가 하락, 불확실성 해소 시 반등 기대.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['반도체 수출', '주가 하락', '시장 상황']</t>
+          <t>['외국인 매도', '기관 매도', '불확실성']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,38 +2580,38 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>192600</v>
+        <v>15040</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-5.12%</t>
+          <t>-3.84%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F24" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G24" t="n">
-        <v>124</v>
+        <v>223</v>
       </c>
       <c r="H24" t="n">
-        <v>75.98999999999999</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,38 +2619,38 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>203000</v>
+        <v>15640</v>
       </c>
       <c r="K24" t="n">
-        <v>195000</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>195600</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>191000</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>75.92</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>359787180200</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>243500</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>58600</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>-852000</v>
+        <v>22000</v>
       </c>
       <c r="S24" t="n">
-        <v>-123000</v>
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>미국 증시 하락 및 기관/외인 매도세로 주가 하락 압력을 받으며, 배당금 대비 주가 하락에 대한 불만이 나타남.</t>
+          <t>금호건설, 호남 반도체 부지 100만평 추가 확보 검토 및 삼성전자 신축 공장 수주 소식. 친환경 및 폐기물 처리 사업 관련 성장성 기대.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['우선주', '기관 매도', '미국 증시']</t>
+          <t>['반도체 부지', '신축 공장 수주', '친환경']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,191 +2672,191 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3560</v>
+        <v>258000</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-7.89%</t>
+          <t>-4.09%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="E25" t="n">
-        <v>49</v>
+        <v>800</v>
       </c>
       <c r="F25" t="n">
-        <v>31</v>
+        <v>507</v>
       </c>
       <c r="G25" t="n">
-        <v>96</v>
+        <v>1581</v>
       </c>
       <c r="H25" t="n">
-        <v>0.73</v>
+        <v>46.71</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>3865</v>
+        <v>269000</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>258000</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>257000</v>
       </c>
       <c r="N25" t="n">
-        <v>1.54</v>
+        <v>46.81</v>
       </c>
       <c r="O25" t="n">
-        <v>38116000000</v>
+        <v>1846633524750</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>72100</v>
       </c>
       <c r="R25" t="n">
-        <v>64000</v>
+        <v>-1232000</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>-646000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 투자자들의 불안 심리가 관찰됨. 일부 긍정적인 전망도 있으나, 5일선 붕괴 등 하락 추세를 나타냄.</t>
+          <t>반도체 수출 역대 최대에도 불구하고 주가 하락, 개인 투자자 완전 승리 전망.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['폭락', '주주', '전망']</t>
+          <t>['반도체 수출', '주가 하락', '개인 투자자']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>233000</v>
+        <v>9280</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-7.91%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.96</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>198</v>
+        <v>64</v>
       </c>
       <c r="F26" t="n">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="G26" t="n">
-        <v>678</v>
+        <v>280</v>
       </c>
       <c r="H26" t="n">
-        <v>7.58</v>
+        <v>4.49</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>253000</v>
+        <v>9800</v>
       </c>
       <c r="K26" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>231000</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>8.539999999999999</v>
+        <v>4.42</v>
       </c>
       <c r="O26" t="n">
-        <v>163918301750</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>426000</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>86100</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>-298000</v>
+        <v>-88000</v>
       </c>
       <c r="S26" t="n">
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>기관의 꾸준한 매수에도 불구하고 주가 하락. 공매도에 대한 불만 및 주가 방어 요구.</t>
+          <t>바이오니아, 프리갈리앙 베스트 의료기술상 수상. 역대급 거래량 및 물량 증가세 확인. 탈모 치료제 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['공매도', '기관매수', '주가방어']</t>
+          <t>['의료 기술상', '프리갈리앙', '탈모']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
@@ -2867,24 +2867,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27350</v>
+        <v>27400</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-9.74%</t>
+          <t>-9.57%</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>-0.01</v>
       </c>
       <c r="E27" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="F27" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G27" t="n">
-        <v>351</v>
+        <v>376</v>
       </c>
       <c r="H27" t="n">
         <v>0.32</v>
@@ -2910,7 +2910,7 @@
         <v>0.33</v>
       </c>
       <c r="O27" t="n">
-        <v>291382000000</v>
+        <v>292465000000</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2926,16 +2926,16 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>신규 상장주로서의 스카이랩스에 대한 기대감. 외인 수급 및 단기 급등 가능성 언급.</t>
+          <t>외국인 매수세 유입, 하락장 속 다른 급등주 자금 유입 가능성 언급.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['신규주', '외인 수급', '단기 급등']</t>
+          <t>['외국인', '하락장', '자금 유입']</t>
         </is>
       </c>
       <c r="X27" t="n">
